--- a/model/Output_Budget/1. Baseline/Grid Search/Output Files/750000/Output_2_11.xlsx
+++ b/model/Output_Budget/1. Baseline/Grid Search/Output Files/750000/Output_2_11.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>319650.2816502029</v>
+        <v>300771.3271433048</v>
       </c>
     </row>
     <row r="7">
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2995127.424547405</v>
+        <v>3013503.893776012</v>
       </c>
     </row>
     <row r="8">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>20355556.36745723</v>
+        <v>20373567.1449482</v>
       </c>
     </row>
     <row r="9">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4813076.283068547</v>
+        <v>4789718.594510994</v>
       </c>
     </row>
     <row r="11">
@@ -1135,16 +1135,16 @@
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>0.9608114308426601</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>11.94928935461252</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -1165,10 +1165,10 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>9.990699214544804</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -1217,13 +1217,13 @@
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>22.15420867374214</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>0.7465913262578567</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -1247,10 +1247,10 @@
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
         <v>0</v>
@@ -1320,19 +1320,19 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>2.721440735106512</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>19.82224313344376</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
         <v>0</v>
@@ -1402,19 +1402,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>9.990699214544804</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>12.91010078545518</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1448,16 +1448,16 @@
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>22.90079999999999</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1539,10 +1539,10 @@
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>22.26949182588285</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -1566,13 +1566,13 @@
         <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>0.2741920426674171</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1594,7 +1594,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
         <v>0</v>
@@ -1606,7 +1606,7 @@
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -1648,7 +1648,7 @@
         <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>22.90079999999999</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
         <v>0</v>
@@ -1663,7 +1663,7 @@
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1685,19 +1685,19 @@
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>22.15420867374215</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>0.7465913262578567</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
@@ -1779,7 +1779,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>22.26949182588285</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -1794,16 +1794,16 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>0.2741920426674241</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
         <v>0</v>
@@ -1876,25 +1876,25 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="T17" t="n">
-        <v>24.66239999999999</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="U17" t="n">
-        <v>28</v>
+        <v>14.31059503474164</v>
       </c>
       <c r="V17" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
@@ -1928,13 +1928,13 @@
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>0.7465913262578567</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
@@ -1958,16 +1958,16 @@
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>28</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="S18" t="n">
-        <v>28</v>
+        <v>23.55470292302859</v>
       </c>
       <c r="T18" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>24.66239999999999</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -2034,16 +2034,16 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>28</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="R19" t="n">
-        <v>28</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="S19" t="n">
-        <v>28</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="T19" t="n">
-        <v>22.02246762618611</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
         <v>0</v>
@@ -2052,7 +2052,7 @@
         <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>22.44875936050941</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
@@ -2071,7 +2071,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
@@ -2083,10 +2083,10 @@
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="H20" t="n">
-        <v>29.74100271005999</v>
+        <v>103.0088977318019</v>
       </c>
       <c r="I20" t="n">
         <v>210.4758895704059</v>
@@ -2116,13 +2116,13 @@
         <v>9.990699214544804</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>149.8691179411497</v>
       </c>
       <c r="S20" t="n">
         <v>209.0200695862453</v>
       </c>
       <c r="T20" t="n">
-        <v>223.0958495641314</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
         <v>0</v>
@@ -2156,22 +2156,22 @@
         <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>157.6450804554009</v>
+        <v>0</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>97.72535009664429</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>112.2354442364965</v>
+        <v>104.7383832473596</v>
       </c>
       <c r="I21" t="n">
-        <v>89.39663285141508</v>
+        <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>0.7465913262578567</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
@@ -2195,19 +2195,19 @@
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>100.1578341526431</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
         <v>171.6831711038378</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>200.1647286948216</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>225.9413820809748</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>232.8005871494253</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
@@ -2216,7 +2216,7 @@
         <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>205.6826957773044</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -2226,7 +2226,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>133.186967585368</v>
+        <v>0</v>
       </c>
       <c r="C22" t="n">
         <v>0</v>
@@ -2271,10 +2271,10 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>86.16204325169439</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>47.02492433367365</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -2314,7 +2314,7 @@
         <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
@@ -2323,10 +2323,10 @@
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>230.8476210749816</v>
+        <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>210.4758895704059</v>
+        <v>200.3360962888296</v>
       </c>
       <c r="J23" t="n">
         <v>11.94928935461252</v>
@@ -2362,10 +2362,10 @@
         <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="V23" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
@@ -2393,7 +2393,7 @@
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>157.6450804554009</v>
+        <v>0</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
@@ -2402,10 +2402,10 @@
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>112.2354442364965</v>
+        <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>87.40341067745341</v>
+        <v>70.84795259427446</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2432,16 +2432,16 @@
         <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>100.1578341526431</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>171.6831711038378</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>200.1647286948216</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>225.9413820809748</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2450,10 +2450,10 @@
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>205.7729852034775</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>205.6826957773044</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -2484,13 +2484,13 @@
         <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>17.55829564281238</v>
+        <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>93.35918011667277</v>
+        <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>22.26949182588285</v>
+        <v>0</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
@@ -2532,7 +2532,7 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>133.186967585368</v>
       </c>
     </row>
     <row r="26">
@@ -2587,31 +2587,31 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>149.8691179411497</v>
       </c>
       <c r="S26" t="n">
-        <v>209.0200695862453</v>
+        <v>70.34400780127524</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>223.0958495641314</v>
       </c>
       <c r="U26" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="X26" t="n">
-        <v>3.252730413754638</v>
+        <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
     </row>
     <row r="27">
@@ -2621,16 +2621,16 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0</v>
+        <v>166.5331836498673</v>
       </c>
       <c r="C27" t="n">
-        <v>45.23342185655322</v>
+        <v>0</v>
       </c>
       <c r="D27" t="n">
-        <v>147.4450655646388</v>
+        <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>157.6450804554009</v>
+        <v>0</v>
       </c>
       <c r="F27" t="n">
         <v>145.0692123933839</v>
@@ -2639,10 +2639,10 @@
         <v>137.3435171632106</v>
       </c>
       <c r="H27" t="n">
-        <v>112.2354442364965</v>
+        <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>89.39663285141508</v>
+        <v>79.78832327157352</v>
       </c>
       <c r="J27" t="n">
         <v>0.7465913262578567</v>
@@ -2669,13 +2669,13 @@
         <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>100.1578341526431</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>200.1647286948216</v>
       </c>
       <c r="U27" t="n">
         <v>0</v>
@@ -2690,7 +2690,7 @@
         <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>205.6826957773044</v>
       </c>
     </row>
     <row r="28">
@@ -2727,7 +2727,7 @@
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>22.26949182588285</v>
+        <v>0</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
@@ -2757,10 +2757,10 @@
         <v>0</v>
       </c>
       <c r="U28" t="n">
-        <v>110.9174757594852</v>
+        <v>0</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>133.186967585368</v>
       </c>
       <c r="W28" t="n">
         <v>0</v>
@@ -2794,7 +2794,7 @@
         <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>230.2038249569697</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
@@ -2827,10 +2827,10 @@
         <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>21.15688084962317</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>209.0200695862453</v>
+        <v>0</v>
       </c>
       <c r="T29" t="n">
         <v>223.0958495641314</v>
@@ -2839,16 +2839,16 @@
         <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
     </row>
     <row r="30">
@@ -2858,28 +2858,28 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0</v>
+        <v>166.5331836498673</v>
       </c>
       <c r="C30" t="n">
-        <v>146.1378473354543</v>
+        <v>172.7084989883157</v>
       </c>
       <c r="D30" t="n">
         <v>147.4450655646388</v>
       </c>
       <c r="E30" t="n">
-        <v>157.6450804554009</v>
+        <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>145.0692123933839</v>
+        <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>137.3435171632106</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>112.2354442364965</v>
+        <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>89.39663285141508</v>
+        <v>0</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2906,7 +2906,7 @@
         <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>37.18582309281555</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -2924,10 +2924,10 @@
         <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>205.7729852034775</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>205.6826957773044</v>
       </c>
     </row>
     <row r="31">
@@ -2955,16 +2955,16 @@
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>133.186967585368</v>
       </c>
       <c r="I31" t="n">
-        <v>17.55829564281238</v>
+        <v>0</v>
       </c>
       <c r="J31" t="n">
-        <v>93.35918011667277</v>
+        <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>22.26949182588285</v>
+        <v>0</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
@@ -3022,10 +3022,10 @@
         <v>0</v>
       </c>
       <c r="D32" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="E32" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="F32" t="n">
         <v>0</v>
@@ -3061,25 +3061,25 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>9.990699214544804</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>149.8691179411497</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>29.51218284430547</v>
+        <v>0</v>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>212.285385643442</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="V32" t="n">
-        <v>215</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="W32" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="X32" t="n">
         <v>0</v>
@@ -3095,31 +3095,31 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>166.5331836498673</v>
+        <v>0</v>
       </c>
       <c r="C33" t="n">
-        <v>0</v>
+        <v>172.7084989883157</v>
       </c>
       <c r="D33" t="n">
         <v>0</v>
       </c>
       <c r="E33" t="n">
-        <v>0</v>
+        <v>77.66362662251787</v>
       </c>
       <c r="F33" t="n">
-        <v>0</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H33" t="n">
-        <v>0</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="I33" t="n">
         <v>89.39663285141508</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>0.7465913262578567</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
@@ -3146,13 +3146,13 @@
         <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>157.7594877214132</v>
+        <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>200.1647286948216</v>
       </c>
       <c r="U33" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="V33" t="n">
         <v>0</v>
@@ -3164,7 +3164,7 @@
         <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>205.6826957773044</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -3195,13 +3195,13 @@
         <v>0</v>
       </c>
       <c r="I34" t="n">
-        <v>0</v>
+        <v>17.55829564281241</v>
       </c>
       <c r="J34" t="n">
-        <v>0</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="K34" t="n">
-        <v>0</v>
+        <v>22.26949182588285</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
@@ -3216,16 +3216,16 @@
         <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>2.721440735106512</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>86.16204325169439</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
         <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>44.30348359856713</v>
+        <v>0</v>
       </c>
       <c r="T34" t="n">
         <v>0</v>
@@ -3256,10 +3256,10 @@
         <v>0</v>
       </c>
       <c r="C35" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="D35" t="n">
-        <v>189.3719999999999</v>
+        <v>0</v>
       </c>
       <c r="E35" t="n">
         <v>0</v>
@@ -3310,19 +3310,19 @@
         <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>212.285385643442</v>
       </c>
       <c r="V35" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="Y35" t="n">
-        <v>215</v>
+        <v>241.0142888776591</v>
       </c>
     </row>
     <row r="36">
@@ -3341,16 +3341,16 @@
         <v>0</v>
       </c>
       <c r="E36" t="n">
-        <v>0</v>
+        <v>157.6450804554009</v>
       </c>
       <c r="F36" t="n">
         <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>29.28483259751476</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>112.2354442364965</v>
+        <v>47.87577769639576</v>
       </c>
       <c r="I36" t="n">
         <v>89.39663285141508</v>
@@ -3389,13 +3389,13 @@
         <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>215</v>
+        <v>225.9413820809748</v>
       </c>
       <c r="V36" t="n">
         <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>215</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="X36" t="n">
         <v>0</v>
@@ -3420,7 +3420,7 @@
         <v>0</v>
       </c>
       <c r="E37" t="n">
-        <v>0</v>
+        <v>133.186967585368</v>
       </c>
       <c r="F37" t="n">
         <v>0</v>
@@ -3462,7 +3462,7 @@
         <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>133.186967585368</v>
+        <v>0</v>
       </c>
       <c r="T37" t="n">
         <v>0</v>
@@ -3505,16 +3505,16 @@
         <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="H38" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="I38" t="n">
-        <v>189.3719999999999</v>
+        <v>210.4758895704059</v>
       </c>
       <c r="J38" t="n">
-        <v>0</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="K38" t="n">
         <v>0</v>
@@ -3535,19 +3535,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>149.8691179411497</v>
       </c>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>71.01467844038818</v>
       </c>
       <c r="T38" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="U38" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="V38" t="n">
         <v>0</v>
@@ -3559,7 +3559,7 @@
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -3572,19 +3572,19 @@
         <v>0</v>
       </c>
       <c r="C39" t="n">
-        <v>172.7084989883157</v>
+        <v>0</v>
       </c>
       <c r="D39" t="n">
-        <v>147.4450655646388</v>
+        <v>0</v>
       </c>
       <c r="E39" t="n">
-        <v>157.6450804554009</v>
+        <v>0</v>
       </c>
       <c r="F39" t="n">
-        <v>145.0692123933839</v>
+        <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>11.33941390343902</v>
+        <v>0</v>
       </c>
       <c r="H39" t="n">
         <v>0</v>
@@ -3620,22 +3620,22 @@
         <v>0</v>
       </c>
       <c r="S39" t="n">
-        <v>0</v>
+        <v>171.6831711038378</v>
       </c>
       <c r="T39" t="n">
-        <v>200.1647286948216</v>
+        <v>99.13012673870382</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>225.9413820809748</v>
       </c>
       <c r="V39" t="n">
-        <v>0</v>
+        <v>232.8005871494253</v>
       </c>
       <c r="W39" t="n">
         <v>0</v>
       </c>
       <c r="X39" t="n">
-        <v>0</v>
+        <v>205.7729852034775</v>
       </c>
       <c r="Y39" t="n">
         <v>0</v>
@@ -3654,7 +3654,7 @@
         <v>0</v>
       </c>
       <c r="D40" t="n">
-        <v>0</v>
+        <v>133.186967585368</v>
       </c>
       <c r="E40" t="n">
         <v>0</v>
@@ -3705,7 +3705,7 @@
         <v>0</v>
       </c>
       <c r="U40" t="n">
-        <v>133.186967585368</v>
+        <v>0</v>
       </c>
       <c r="V40" t="n">
         <v>0</v>
@@ -3733,13 +3733,13 @@
         <v>0</v>
       </c>
       <c r="D41" t="n">
-        <v>0</v>
+        <v>213.4242636173429</v>
       </c>
       <c r="E41" t="n">
-        <v>213</v>
+        <v>0</v>
       </c>
       <c r="F41" t="n">
-        <v>0</v>
+        <v>213.4242636173429</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -3772,7 +3772,7 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R41" t="n">
         <v>0</v>
@@ -3781,16 +3781,16 @@
         <v>0</v>
       </c>
       <c r="T41" t="n">
-        <v>0</v>
+        <v>177.9933921796108</v>
       </c>
       <c r="U41" t="n">
-        <v>187.6104</v>
+        <v>0</v>
       </c>
       <c r="V41" t="n">
-        <v>213</v>
+        <v>213.4242636173429</v>
       </c>
       <c r="W41" t="n">
-        <v>213</v>
+        <v>0</v>
       </c>
       <c r="X41" t="n">
         <v>0</v>
@@ -3812,19 +3812,19 @@
         <v>0</v>
       </c>
       <c r="D42" t="n">
-        <v>147.4450655646388</v>
+        <v>0</v>
       </c>
       <c r="E42" t="n">
-        <v>71.5171606422703</v>
+        <v>66.03342048484895</v>
       </c>
       <c r="F42" t="n">
-        <v>145.0692123933839</v>
+        <v>0</v>
       </c>
       <c r="G42" t="n">
         <v>137.3435171632106</v>
       </c>
       <c r="H42" t="n">
-        <v>112.2354442364965</v>
+        <v>0</v>
       </c>
       <c r="I42" t="n">
         <v>0</v>
@@ -3863,19 +3863,19 @@
         <v>0</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>213.4242636173429</v>
       </c>
       <c r="V42" t="n">
         <v>0</v>
       </c>
       <c r="W42" t="n">
-        <v>213</v>
+        <v>0</v>
       </c>
       <c r="X42" t="n">
-        <v>0</v>
+        <v>205.7729852034775</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>205.6826957773044</v>
       </c>
     </row>
     <row r="43">
@@ -3948,13 +3948,13 @@
         <v>0</v>
       </c>
       <c r="W43" t="n">
-        <v>0</v>
+        <v>133.186967585368</v>
       </c>
       <c r="X43" t="n">
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>133.186967585368</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -4763,76 +4763,76 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>67.64575836914665</v>
+        <v>0</v>
       </c>
       <c r="C8" t="n">
-        <v>67.64575836914665</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>67.64575836914665</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>67.64575836914665</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>67.64575836914665</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>66.67524177233588</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>40.41261550970962</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>14.14998924708335</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>27.82</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>52.52000000000001</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>78.26000000000001</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>93.90838463177292</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>67.64575836914665</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>67.64575836914665</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>67.64575836914665</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>67.64575836914665</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>67.64575836914665</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>67.64575836914665</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>67.64575836914665</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>67.64575836914665</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -4842,76 +4842,76 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>51.47474747474747</v>
+        <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>51.47474747474747</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>51.47474747474747</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>51.47474747474747</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>51.47474747474747</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>51.47474747474747</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>29.09675891541198</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>2.834132652785714</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>27.82</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>53.56</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>78.26000000000001</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>78.26000000000001</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>77.73737373737373</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>51.47474747474747</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>51.47474747474747</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>51.47474747474747</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>51.47474747474747</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>51.47474747474747</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>51.47474747474747</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>51.47474747474747</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -4921,76 +4921,76 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.44072336510073</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>2.44072336510073</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>2.44072336510073</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>2.44072336510073</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>2.44072336510073</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>2.44072336510073</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>2.44072336510073</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>2.44072336510073</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>2.44072336510073</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>2.44072336510073</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>28.18072336510073</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>53.92072336510073</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>79.66072336510072</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>101.2510699645389</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>74.98844370191262</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>48.72581743928635</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>22.46319117666009</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>2.44072336510073</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>2.44072336510073</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>2.44072336510073</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>2.44072336510073</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>2.44072336510073</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.44072336510073</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -5000,76 +5000,76 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>26.78000000000001</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>52.52000000000001</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>78.26000000000001</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>78.26000000000001</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>93.90838463177292</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>67.64575836914665</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>41.38313210652039</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>15.12050584389412</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -5079,76 +5079,76 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>80.86787878787879</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>54.60525252525252</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>28.34262626262626</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>27.82</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>53.56</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>53.56</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>53.56</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>78.26000000000001</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -5158,76 +5158,76 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>51.19778581548745</v>
+        <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>51.19778581548745</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>51.19778581548745</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>51.19778581548745</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>51.19778581548745</v>
+        <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>51.19778581548745</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>51.19778581548745</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>51.19778581548745</v>
+        <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>24.93515955286119</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>2.44072336510073</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>28.18072336510073</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>53.92072336510073</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>79.66072336510072</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>77.73737373737373</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>51.47474747474747</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>51.19778581548745</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>51.19778581548745</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>51.19778581548745</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>51.19778581548745</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>51.19778581548745</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -5237,76 +5237,76 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>28.34262626262626</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>28.34262626262626</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>28.34262626262626</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>28.34262626262626</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>27.82</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>53.56</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>53.56</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>53.56</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>78.26000000000001</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>80.86787878787879</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>80.86787878787879</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>80.86787878787879</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>80.86787878787879</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>80.86787878787879</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>54.60525252525252</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -5316,76 +5316,76 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>81.62201144066449</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>55.35938517803824</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>29.09675891541198</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>2.834132652785714</v>
+        <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>26.78000000000001</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>26.78000000000001</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>52.52000000000001</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>78.26000000000001</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -5395,76 +5395,76 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>24.93515955286119</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>24.93515955286119</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>24.93515955286119</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>24.93515955286119</v>
+        <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>24.93515955286119</v>
+        <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>24.93515955286119</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>24.93515955286119</v>
+        <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>24.93515955286119</v>
+        <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>24.93515955286119</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>2.44072336510073</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>28.18072336510073</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>53.92072336510073</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>79.66072336510072</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>103.72303834074</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>77.46041207811371</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>51.19778581548745</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>24.93515955286119</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>24.93515955286119</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>24.93515955286119</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>24.93515955286119</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>24.93515955286119</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>24.93515955286119</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>24.93515955286119</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -5474,76 +5474,76 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="C17" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="D17" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="E17" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="F17" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="G17" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="H17" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="I17" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="J17" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="K17" t="n">
-        <v>2.24</v>
+        <v>28.41772601812563</v>
       </c>
       <c r="L17" t="n">
-        <v>2.24</v>
+        <v>28.41772601812563</v>
       </c>
       <c r="M17" t="n">
-        <v>28.84</v>
+        <v>55.73185102583861</v>
       </c>
       <c r="N17" t="n">
-        <v>56.56</v>
+        <v>83.04597603355158</v>
       </c>
       <c r="O17" t="n">
-        <v>84.28</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="P17" t="n">
-        <v>112</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="Q17" t="n">
-        <v>112</v>
+        <v>100.2684856730375</v>
       </c>
       <c r="R17" t="n">
-        <v>112</v>
+        <v>72.39977328887976</v>
       </c>
       <c r="S17" t="n">
-        <v>112</v>
+        <v>44.53106090472204</v>
       </c>
       <c r="T17" t="n">
-        <v>87.08848484848485</v>
+        <v>16.66234852056432</v>
       </c>
       <c r="U17" t="n">
-        <v>58.80565656565657</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="V17" t="n">
-        <v>30.52282828282829</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="W17" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="X17" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="Y17" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
     </row>
     <row r="18">
@@ -5553,76 +5553,76 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.24</v>
+        <v>58.69875944192644</v>
       </c>
       <c r="C18" t="n">
-        <v>2.24</v>
+        <v>58.69875944192644</v>
       </c>
       <c r="D18" t="n">
-        <v>2.24</v>
+        <v>58.69875944192644</v>
       </c>
       <c r="E18" t="n">
-        <v>2.24</v>
+        <v>58.69875944192644</v>
       </c>
       <c r="F18" t="n">
-        <v>2.24</v>
+        <v>58.69875944192644</v>
       </c>
       <c r="G18" t="n">
-        <v>2.24</v>
+        <v>58.69875944192644</v>
       </c>
       <c r="H18" t="n">
-        <v>2.24</v>
+        <v>30.83004705776872</v>
       </c>
       <c r="I18" t="n">
-        <v>2.24</v>
+        <v>2.961334673611005</v>
       </c>
       <c r="J18" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="K18" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="L18" t="n">
-        <v>2.24</v>
+        <v>28.41772601812563</v>
       </c>
       <c r="M18" t="n">
-        <v>2.24</v>
+        <v>28.41772601812563</v>
       </c>
       <c r="N18" t="n">
-        <v>28.84</v>
+        <v>55.73185102583861</v>
       </c>
       <c r="O18" t="n">
-        <v>56.56</v>
+        <v>83.04597603355158</v>
       </c>
       <c r="P18" t="n">
-        <v>84.28</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="Q18" t="n">
-        <v>112</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="R18" t="n">
-        <v>83.71717171717171</v>
+        <v>82.49138865710684</v>
       </c>
       <c r="S18" t="n">
-        <v>55.43434343434343</v>
+        <v>58.69875944192644</v>
       </c>
       <c r="T18" t="n">
-        <v>27.15151515151514</v>
+        <v>58.69875944192644</v>
       </c>
       <c r="U18" t="n">
-        <v>2.24</v>
+        <v>58.69875944192644</v>
       </c>
       <c r="V18" t="n">
-        <v>2.24</v>
+        <v>58.69875944192644</v>
       </c>
       <c r="W18" t="n">
-        <v>2.24</v>
+        <v>58.69875944192644</v>
       </c>
       <c r="X18" t="n">
-        <v>2.24</v>
+        <v>58.69875944192644</v>
       </c>
       <c r="Y18" t="n">
-        <v>2.24</v>
+        <v>58.69875944192644</v>
       </c>
     </row>
     <row r="19">
@@ -5632,76 +5632,76 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="C19" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="D19" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="E19" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="F19" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="G19" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="H19" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="I19" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="J19" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="K19" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="L19" t="n">
-        <v>29.55412500771298</v>
+        <v>29.52132702853827</v>
       </c>
       <c r="M19" t="n">
-        <v>57.27412500771297</v>
+        <v>56.83545203625125</v>
       </c>
       <c r="N19" t="n">
-        <v>84.99412500771297</v>
+        <v>84.14957704396423</v>
       </c>
       <c r="O19" t="n">
-        <v>109.3334016426122</v>
+        <v>108.4888536788635</v>
       </c>
       <c r="P19" t="n">
-        <v>109.3334016426122</v>
+        <v>108.4888536788635</v>
       </c>
       <c r="Q19" t="n">
-        <v>81.05057335978395</v>
+        <v>80.62014129470579</v>
       </c>
       <c r="R19" t="n">
-        <v>52.76774507695567</v>
+        <v>52.75142891054807</v>
       </c>
       <c r="S19" t="n">
-        <v>24.48491679412739</v>
+        <v>24.88271652639035</v>
       </c>
       <c r="T19" t="n">
-        <v>2.24</v>
+        <v>24.88271652639035</v>
       </c>
       <c r="U19" t="n">
-        <v>2.24</v>
+        <v>24.88271652639035</v>
       </c>
       <c r="V19" t="n">
-        <v>2.24</v>
+        <v>24.88271652639035</v>
       </c>
       <c r="W19" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="X19" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="Y19" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
     </row>
     <row r="20">
@@ -5711,76 +5711,76 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>517.427658217251</v>
+        <v>591.4512093066566</v>
       </c>
       <c r="C20" t="n">
-        <v>273.9933147829075</v>
+        <v>591.4512093066566</v>
       </c>
       <c r="D20" t="n">
-        <v>273.9933147829075</v>
+        <v>591.4512093066566</v>
       </c>
       <c r="E20" t="n">
-        <v>273.9933147829075</v>
+        <v>591.4512093066566</v>
       </c>
       <c r="F20" t="n">
-        <v>273.9933147829075</v>
+        <v>591.4512093066566</v>
       </c>
       <c r="G20" t="n">
-        <v>273.9933147829075</v>
+        <v>348.0024326625565</v>
       </c>
       <c r="H20" t="n">
-        <v>243.9518979040591</v>
+        <v>243.9530410142718</v>
       </c>
       <c r="I20" t="n">
-        <v>31.34998924708335</v>
+        <v>31.35113235729608</v>
       </c>
       <c r="J20" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K20" t="n">
-        <v>122.2950059109224</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L20" t="n">
-        <v>302.3708574955809</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M20" t="n">
-        <v>519.3464847584851</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N20" t="n">
-        <v>725.2010069657244</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O20" t="n">
-        <v>874.3959571083725</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P20" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q20" t="n">
-        <v>953.9083846317729</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="R20" t="n">
-        <v>953.9083846317729</v>
+        <v>802.5825927271064</v>
       </c>
       <c r="S20" t="n">
-        <v>742.7770012113231</v>
+        <v>591.4512093066566</v>
       </c>
       <c r="T20" t="n">
-        <v>517.427658217251</v>
+        <v>591.4512093066566</v>
       </c>
       <c r="U20" t="n">
-        <v>517.427658217251</v>
+        <v>591.4512093066566</v>
       </c>
       <c r="V20" t="n">
-        <v>517.427658217251</v>
+        <v>591.4512093066566</v>
       </c>
       <c r="W20" t="n">
-        <v>517.427658217251</v>
+        <v>591.4512093066566</v>
       </c>
       <c r="X20" t="n">
-        <v>517.427658217251</v>
+        <v>591.4512093066566</v>
       </c>
       <c r="Y20" t="n">
-        <v>517.427658217251</v>
+        <v>591.4512093066566</v>
       </c>
     </row>
     <row r="21">
@@ -5790,76 +5790,76 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>481.6528272386007</v>
+        <v>125.0774898247174</v>
       </c>
       <c r="C21" t="n">
-        <v>481.6528272386007</v>
+        <v>125.0774898247174</v>
       </c>
       <c r="D21" t="n">
-        <v>481.6528272386007</v>
+        <v>125.0774898247174</v>
       </c>
       <c r="E21" t="n">
-        <v>322.4153722331451</v>
+        <v>125.0774898247174</v>
       </c>
       <c r="F21" t="n">
-        <v>322.4153722331451</v>
+        <v>125.0774898247174</v>
       </c>
       <c r="G21" t="n">
-        <v>223.7028973880499</v>
+        <v>125.0774898247174</v>
       </c>
       <c r="H21" t="n">
-        <v>110.3337617956292</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I21" t="n">
-        <v>20.03413265278571</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J21" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K21" t="n">
-        <v>144.6375600578374</v>
+        <v>144.6387031680501</v>
       </c>
       <c r="L21" t="n">
-        <v>374.6006659261865</v>
+        <v>144.6387031680501</v>
       </c>
       <c r="M21" t="n">
-        <v>613.1906659261865</v>
+        <v>234.810827406191</v>
       </c>
       <c r="N21" t="n">
-        <v>851.7806659261865</v>
+        <v>473.4149733950735</v>
       </c>
       <c r="O21" t="n">
-        <v>964</v>
+        <v>712.019119383956</v>
       </c>
       <c r="P21" t="n">
-        <v>964</v>
+        <v>894.6625969973069</v>
       </c>
       <c r="Q21" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R21" t="n">
-        <v>862.8304705528857</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S21" t="n">
-        <v>689.4131260035546</v>
+        <v>790.6398109613051</v>
       </c>
       <c r="T21" t="n">
-        <v>689.4131260035546</v>
+        <v>588.4532163200711</v>
       </c>
       <c r="U21" t="n">
-        <v>689.4131260035546</v>
+        <v>360.2295980564601</v>
       </c>
       <c r="V21" t="n">
-        <v>689.4131260035546</v>
+        <v>125.0774898247174</v>
       </c>
       <c r="W21" t="n">
-        <v>689.4131260035546</v>
+        <v>125.0774898247174</v>
       </c>
       <c r="X21" t="n">
-        <v>689.4131260035546</v>
+        <v>125.0774898247174</v>
       </c>
       <c r="Y21" t="n">
-        <v>481.6528272386007</v>
+        <v>125.0774898247174</v>
       </c>
     </row>
     <row r="22">
@@ -5869,76 +5869,76 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C22" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D22" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E22" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F22" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G22" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H22" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I22" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J22" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K22" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L22" t="n">
-        <v>46.59412500771298</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M22" t="n">
-        <v>85.78216319993516</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N22" t="n">
-        <v>129.4730138553714</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O22" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P22" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Q22" t="n">
-        <v>153.8122904902707</v>
+        <v>66.78106667958005</v>
       </c>
       <c r="R22" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="S22" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="T22" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="U22" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="V22" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="W22" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="X22" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="Y22" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
     <row r="23">
@@ -5948,76 +5948,76 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>720.5656565656566</v>
+        <v>477.1596022224361</v>
       </c>
       <c r="C23" t="n">
-        <v>720.5656565656566</v>
+        <v>477.1596022224361</v>
       </c>
       <c r="D23" t="n">
-        <v>720.5656565656566</v>
+        <v>477.1596022224361</v>
       </c>
       <c r="E23" t="n">
-        <v>477.1313131313132</v>
+        <v>233.7108255783361</v>
       </c>
       <c r="F23" t="n">
-        <v>477.1313131313132</v>
+        <v>233.7108255783361</v>
       </c>
       <c r="G23" t="n">
-        <v>477.1313131313132</v>
+        <v>233.7108255783361</v>
       </c>
       <c r="H23" t="n">
-        <v>243.9518979040591</v>
+        <v>233.7108255783361</v>
       </c>
       <c r="I23" t="n">
-        <v>31.34998924708335</v>
+        <v>31.35113235729608</v>
       </c>
       <c r="J23" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K23" t="n">
-        <v>122.2389935104989</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L23" t="n">
-        <v>302.3148450951575</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M23" t="n">
-        <v>519.2904723580616</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N23" t="n">
-        <v>725.144994565301</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O23" t="n">
-        <v>874.339944707949</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P23" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q23" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R23" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S23" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T23" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U23" t="n">
-        <v>964</v>
+        <v>720.6083788665362</v>
       </c>
       <c r="V23" t="n">
-        <v>720.5656565656566</v>
+        <v>477.1596022224361</v>
       </c>
       <c r="W23" t="n">
-        <v>720.5656565656566</v>
+        <v>477.1596022224361</v>
       </c>
       <c r="X23" t="n">
-        <v>720.5656565656566</v>
+        <v>477.1596022224361</v>
       </c>
       <c r="Y23" t="n">
-        <v>720.5656565656566</v>
+        <v>477.1596022224361</v>
       </c>
     </row>
     <row r="24">
@@ -6027,76 +6027,76 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>380.1728640094453</v>
+        <v>90.84473158927784</v>
       </c>
       <c r="C24" t="n">
-        <v>380.1728640094453</v>
+        <v>90.84473158927784</v>
       </c>
       <c r="D24" t="n">
-        <v>380.1728640094453</v>
+        <v>90.84473158927784</v>
       </c>
       <c r="E24" t="n">
-        <v>220.9354090039898</v>
+        <v>90.84473158927784</v>
       </c>
       <c r="F24" t="n">
-        <v>220.9354090039898</v>
+        <v>90.84473158927784</v>
       </c>
       <c r="G24" t="n">
-        <v>220.9354090039898</v>
+        <v>90.84473158927784</v>
       </c>
       <c r="H24" t="n">
-        <v>107.5662734115691</v>
+        <v>90.84473158927784</v>
       </c>
       <c r="I24" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J24" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K24" t="n">
-        <v>144.6375600578374</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L24" t="n">
-        <v>178.8354414866706</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="M24" t="n">
-        <v>417.4254414866706</v>
+        <v>257.8852890990952</v>
       </c>
       <c r="N24" t="n">
-        <v>656.0154414866706</v>
+        <v>473.4149733950735</v>
       </c>
       <c r="O24" t="n">
-        <v>894.6054414866707</v>
+        <v>712.019119383956</v>
       </c>
       <c r="P24" t="n">
-        <v>894.6054414866707</v>
+        <v>894.6625969973069</v>
       </c>
       <c r="Q24" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R24" t="n">
-        <v>964</v>
+        <v>862.8876260635219</v>
       </c>
       <c r="S24" t="n">
-        <v>964</v>
+        <v>689.4702815141908</v>
       </c>
       <c r="T24" t="n">
-        <v>964</v>
+        <v>487.2836868729568</v>
       </c>
       <c r="U24" t="n">
-        <v>964</v>
+        <v>259.0600686093459</v>
       </c>
       <c r="V24" t="n">
-        <v>964</v>
+        <v>259.0600686093459</v>
       </c>
       <c r="W24" t="n">
-        <v>964</v>
+        <v>259.0600686093459</v>
       </c>
       <c r="X24" t="n">
-        <v>756.1484997944672</v>
+        <v>259.0600686093459</v>
       </c>
       <c r="Y24" t="n">
-        <v>548.3882010295133</v>
+        <v>259.0600686093459</v>
       </c>
     </row>
     <row r="25">
@@ -6106,76 +6106,76 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>964</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C25" t="n">
-        <v>964</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D25" t="n">
-        <v>964</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E25" t="n">
-        <v>964</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F25" t="n">
-        <v>964</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G25" t="n">
-        <v>964</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H25" t="n">
-        <v>964</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I25" t="n">
-        <v>946.264347835543</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J25" t="n">
-        <v>851.9621456974897</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K25" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L25" t="n">
-        <v>856.7818345174422</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M25" t="n">
-        <v>895.9698727096644</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N25" t="n">
-        <v>939.6607233651007</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O25" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P25" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Q25" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="R25" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="S25" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="T25" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="U25" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="V25" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="W25" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="X25" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Y25" t="n">
-        <v>964</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
     <row r="26">
@@ -6185,76 +6185,76 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C26" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D26" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E26" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F26" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G26" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H26" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I26" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J26" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K26" t="n">
-        <v>122.2950059109224</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L26" t="n">
-        <v>302.3708574955809</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M26" t="n">
-        <v>519.3464847584851</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N26" t="n">
-        <v>725.2010069657244</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O26" t="n">
-        <v>874.3959571083725</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P26" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q26" t="n">
-        <v>964</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="R26" t="n">
-        <v>964</v>
+        <v>802.5825927271064</v>
       </c>
       <c r="S26" t="n">
-        <v>752.8686165795501</v>
+        <v>731.528039392485</v>
       </c>
       <c r="T26" t="n">
-        <v>752.8686165795501</v>
+        <v>506.1786963984129</v>
       </c>
       <c r="U26" t="n">
-        <v>509.4342731452067</v>
+        <v>506.1786963984129</v>
       </c>
       <c r="V26" t="n">
-        <v>265.9999297108633</v>
+        <v>506.1786963984129</v>
       </c>
       <c r="W26" t="n">
-        <v>22.56558627651984</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="X26" t="n">
-        <v>19.28</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="Y26" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
     <row r="27">
@@ -6264,76 +6264,76 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>862.8304705528857</v>
+        <v>385.8949250843803</v>
       </c>
       <c r="C27" t="n">
-        <v>817.1401454452562</v>
+        <v>385.8949250843803</v>
       </c>
       <c r="D27" t="n">
-        <v>668.2057357840049</v>
+        <v>385.8949250843803</v>
       </c>
       <c r="E27" t="n">
-        <v>508.9682807785495</v>
+        <v>385.8949250843803</v>
       </c>
       <c r="F27" t="n">
-        <v>362.4337228054344</v>
+        <v>239.3603671112653</v>
       </c>
       <c r="G27" t="n">
-        <v>223.7028973880499</v>
+        <v>100.6295416938808</v>
       </c>
       <c r="H27" t="n">
-        <v>110.3337617956292</v>
+        <v>100.6295416938808</v>
       </c>
       <c r="I27" t="n">
-        <v>20.03413265278571</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="J27" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K27" t="n">
-        <v>144.6375600578374</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L27" t="n">
-        <v>144.6375600578374</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="M27" t="n">
-        <v>383.2275600578374</v>
+        <v>257.8852890990952</v>
       </c>
       <c r="N27" t="n">
-        <v>621.8175600578375</v>
+        <v>496.4894350879777</v>
       </c>
       <c r="O27" t="n">
-        <v>781.3565223866492</v>
+        <v>712.019119383956</v>
       </c>
       <c r="P27" t="n">
-        <v>964</v>
+        <v>894.6625969973069</v>
       </c>
       <c r="Q27" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R27" t="n">
-        <v>862.8304705528857</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S27" t="n">
-        <v>862.8304705528857</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T27" t="n">
-        <v>862.8304705528857</v>
+        <v>761.8705608694022</v>
       </c>
       <c r="U27" t="n">
-        <v>862.8304705528857</v>
+        <v>761.8705608694022</v>
       </c>
       <c r="V27" t="n">
-        <v>862.8304705528857</v>
+        <v>761.8705608694022</v>
       </c>
       <c r="W27" t="n">
-        <v>862.8304705528857</v>
+        <v>761.8705608694022</v>
       </c>
       <c r="X27" t="n">
-        <v>862.8304705528857</v>
+        <v>761.8705608694022</v>
       </c>
       <c r="Y27" t="n">
-        <v>862.8304705528857</v>
+        <v>554.1102621044483</v>
       </c>
     </row>
     <row r="28">
@@ -6343,76 +6343,76 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>41.77443618776046</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C28" t="n">
-        <v>41.77443618776046</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D28" t="n">
-        <v>41.77443618776046</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E28" t="n">
-        <v>41.77443618776046</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F28" t="n">
-        <v>41.77443618776046</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G28" t="n">
-        <v>41.77443618776046</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H28" t="n">
-        <v>41.77443618776046</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I28" t="n">
-        <v>41.77443618776046</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J28" t="n">
-        <v>41.77443618776046</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K28" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L28" t="n">
-        <v>46.59412500771298</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M28" t="n">
-        <v>85.78216319993516</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N28" t="n">
-        <v>129.4730138553714</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O28" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P28" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Q28" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="R28" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="S28" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="T28" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="U28" t="n">
-        <v>41.77443618776046</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="V28" t="n">
-        <v>41.77443618776046</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="W28" t="n">
-        <v>41.77443618776046</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="X28" t="n">
-        <v>41.77443618776046</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="Y28" t="n">
-        <v>41.77443618776046</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
     <row r="29">
@@ -6422,76 +6422,76 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>19.28</v>
+        <v>251.810259228364</v>
       </c>
       <c r="C29" t="n">
-        <v>19.28</v>
+        <v>251.810259228364</v>
       </c>
       <c r="D29" t="n">
-        <v>19.28</v>
+        <v>251.810259228364</v>
       </c>
       <c r="E29" t="n">
-        <v>19.28</v>
+        <v>251.810259228364</v>
       </c>
       <c r="F29" t="n">
-        <v>19.28</v>
+        <v>251.810259228364</v>
       </c>
       <c r="G29" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H29" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I29" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J29" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K29" t="n">
-        <v>122.2950059109224</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L29" t="n">
-        <v>302.3708574955809</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M29" t="n">
-        <v>519.3464847584851</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N29" t="n">
-        <v>725.144994565301</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O29" t="n">
-        <v>874.339944707949</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P29" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q29" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R29" t="n">
-        <v>942.6294132832089</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S29" t="n">
-        <v>731.498029862759</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T29" t="n">
-        <v>506.1486868686869</v>
+        <v>738.7078125165641</v>
       </c>
       <c r="U29" t="n">
-        <v>506.1486868686869</v>
+        <v>738.7078125165641</v>
       </c>
       <c r="V29" t="n">
-        <v>262.7143434343434</v>
+        <v>738.7078125165641</v>
       </c>
       <c r="W29" t="n">
-        <v>19.28</v>
+        <v>738.7078125165641</v>
       </c>
       <c r="X29" t="n">
-        <v>19.28</v>
+        <v>495.259035872464</v>
       </c>
       <c r="Y29" t="n">
-        <v>19.28</v>
+        <v>251.810259228364</v>
       </c>
     </row>
     <row r="30">
@@ -6501,76 +6501,76 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>964</v>
+        <v>342.668582052591</v>
       </c>
       <c r="C30" t="n">
-        <v>816.3860127924704</v>
+        <v>168.215552771464</v>
       </c>
       <c r="D30" t="n">
-        <v>667.4516031312191</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E30" t="n">
-        <v>508.2141481257637</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F30" t="n">
-        <v>361.6795901526487</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G30" t="n">
-        <v>222.9487647352642</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H30" t="n">
-        <v>109.5796291428435</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I30" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J30" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K30" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L30" t="n">
-        <v>234.7819638733197</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="M30" t="n">
-        <v>234.7819638733197</v>
+        <v>257.8852890990952</v>
       </c>
       <c r="N30" t="n">
-        <v>473.3719638733197</v>
+        <v>496.4894350879777</v>
       </c>
       <c r="O30" t="n">
-        <v>711.9619638733197</v>
+        <v>712.019119383956</v>
       </c>
       <c r="P30" t="n">
-        <v>894.6054414866707</v>
+        <v>894.6625969973069</v>
       </c>
       <c r="Q30" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R30" t="n">
-        <v>964</v>
+        <v>926.4957180431458</v>
       </c>
       <c r="S30" t="n">
-        <v>964</v>
+        <v>926.4957180431458</v>
       </c>
       <c r="T30" t="n">
-        <v>964</v>
+        <v>926.4957180431458</v>
       </c>
       <c r="U30" t="n">
-        <v>964</v>
+        <v>926.4957180431458</v>
       </c>
       <c r="V30" t="n">
-        <v>964</v>
+        <v>926.4957180431458</v>
       </c>
       <c r="W30" t="n">
-        <v>964</v>
+        <v>926.4957180431458</v>
       </c>
       <c r="X30" t="n">
-        <v>964</v>
+        <v>718.6442178376129</v>
       </c>
       <c r="Y30" t="n">
-        <v>964</v>
+        <v>510.883919072659</v>
       </c>
     </row>
     <row r="31">
@@ -6580,76 +6580,76 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="C31" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="D31" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="E31" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="F31" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="G31" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="H31" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I31" t="n">
-        <v>136.0766383258138</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J31" t="n">
-        <v>41.77443618776046</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K31" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L31" t="n">
-        <v>46.59412500771298</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M31" t="n">
-        <v>85.78216319993516</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N31" t="n">
-        <v>129.4730138553714</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O31" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P31" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Q31" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="R31" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="S31" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="T31" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="U31" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="V31" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="W31" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="X31" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Y31" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
     </row>
     <row r="32">
@@ -6659,76 +6659,76 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>451.5434343434343</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C32" t="n">
-        <v>451.5434343434343</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D32" t="n">
-        <v>234.3717171717172</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E32" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F32" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G32" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H32" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I32" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J32" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K32" t="n">
-        <v>120.2150059109224</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L32" t="n">
-        <v>202.4404723580617</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M32" t="n">
-        <v>415.2904723580617</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N32" t="n">
-        <v>621.144994565301</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O32" t="n">
-        <v>770.339944707949</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P32" t="n">
-        <v>860</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q32" t="n">
-        <v>849.9083846317729</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R32" t="n">
-        <v>698.5254372164702</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S32" t="n">
-        <v>668.7151515151515</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T32" t="n">
-        <v>668.7151515151515</v>
+        <v>749.627473042513</v>
       </c>
       <c r="U32" t="n">
-        <v>668.7151515151515</v>
+        <v>506.1786963984129</v>
       </c>
       <c r="V32" t="n">
-        <v>451.5434343434343</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="W32" t="n">
-        <v>451.5434343434343</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="X32" t="n">
-        <v>451.5434343434343</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="Y32" t="n">
-        <v>451.5434343434343</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
     <row r="33">
@@ -6738,76 +6738,76 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>107.4996291428435</v>
+        <v>761.8705608694022</v>
       </c>
       <c r="C33" t="n">
-        <v>107.4996291428435</v>
+        <v>587.4175315882752</v>
       </c>
       <c r="D33" t="n">
-        <v>107.4996291428435</v>
+        <v>587.4175315882752</v>
       </c>
       <c r="E33" t="n">
-        <v>107.4996291428435</v>
+        <v>508.9694238887622</v>
       </c>
       <c r="F33" t="n">
-        <v>107.4996291428435</v>
+        <v>362.4348659156472</v>
       </c>
       <c r="G33" t="n">
-        <v>107.4996291428435</v>
+        <v>223.7040404982626</v>
       </c>
       <c r="H33" t="n">
-        <v>107.4996291428435</v>
+        <v>110.334904905842</v>
       </c>
       <c r="I33" t="n">
-        <v>17.2</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="J33" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K33" t="n">
-        <v>142.5575600578374</v>
+        <v>144.6387031680501</v>
       </c>
       <c r="L33" t="n">
-        <v>142.5575600578374</v>
+        <v>234.810827406191</v>
       </c>
       <c r="M33" t="n">
-        <v>355.4075600578374</v>
+        <v>473.4149733950735</v>
       </c>
       <c r="N33" t="n">
-        <v>395.1119638733197</v>
+        <v>712.019119383956</v>
       </c>
       <c r="O33" t="n">
-        <v>607.9619638733197</v>
+        <v>712.019119383956</v>
       </c>
       <c r="P33" t="n">
-        <v>790.6054414866707</v>
+        <v>894.6625969973069</v>
       </c>
       <c r="Q33" t="n">
-        <v>860</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R33" t="n">
-        <v>860</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S33" t="n">
-        <v>700.6469820995826</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T33" t="n">
-        <v>700.6469820995826</v>
+        <v>761.8705608694022</v>
       </c>
       <c r="U33" t="n">
-        <v>483.4752649278655</v>
+        <v>761.8705608694022</v>
       </c>
       <c r="V33" t="n">
-        <v>483.4752649278655</v>
+        <v>761.8705608694022</v>
       </c>
       <c r="W33" t="n">
-        <v>483.4752649278655</v>
+        <v>761.8705608694022</v>
       </c>
       <c r="X33" t="n">
-        <v>483.4752649278655</v>
+        <v>761.8705608694022</v>
       </c>
       <c r="Y33" t="n">
-        <v>275.7149661629115</v>
+        <v>761.8705608694022</v>
       </c>
     </row>
     <row r="34">
@@ -6817,76 +6817,76 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>17.2</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="C34" t="n">
-        <v>17.2</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="D34" t="n">
-        <v>17.2</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="E34" t="n">
-        <v>17.2</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="F34" t="n">
-        <v>17.2</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="G34" t="n">
-        <v>17.2</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="H34" t="n">
-        <v>17.2</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="I34" t="n">
-        <v>17.2</v>
+        <v>136.0777814360265</v>
       </c>
       <c r="J34" t="n">
-        <v>17.2</v>
+        <v>41.77557929797318</v>
       </c>
       <c r="K34" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L34" t="n">
-        <v>44.51412500771298</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M34" t="n">
-        <v>83.70216319993516</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N34" t="n">
-        <v>127.3930138553715</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O34" t="n">
-        <v>151.7322904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P34" t="n">
-        <v>148.9833604548096</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Q34" t="n">
-        <v>61.9509935339062</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="R34" t="n">
-        <v>61.9509935339062</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="S34" t="n">
-        <v>17.2</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="T34" t="n">
-        <v>17.2</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="U34" t="n">
-        <v>17.2</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="V34" t="n">
-        <v>17.2</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="W34" t="n">
-        <v>17.2</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="X34" t="n">
-        <v>17.2</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Y34" t="n">
-        <v>17.2</v>
+        <v>153.8134336004835</v>
       </c>
     </row>
     <row r="35">
@@ -6896,76 +6896,76 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>425.6565656565656</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C35" t="n">
-        <v>208.4848484848484</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D35" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E35" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F35" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G35" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H35" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I35" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J35" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K35" t="n">
-        <v>120.2150059109224</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L35" t="n">
-        <v>300.290857495581</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M35" t="n">
-        <v>513.1408574955809</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N35" t="n">
-        <v>718.9953797028202</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O35" t="n">
-        <v>770.339944707949</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P35" t="n">
-        <v>860</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q35" t="n">
-        <v>860</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R35" t="n">
-        <v>860</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S35" t="n">
-        <v>860</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T35" t="n">
-        <v>860</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U35" t="n">
-        <v>860</v>
+        <v>749.627473042513</v>
       </c>
       <c r="V35" t="n">
-        <v>642.8282828282828</v>
+        <v>749.627473042513</v>
       </c>
       <c r="W35" t="n">
-        <v>642.8282828282828</v>
+        <v>506.1786963984129</v>
       </c>
       <c r="X35" t="n">
-        <v>642.8282828282828</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="Y35" t="n">
-        <v>425.6565656565656</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
     <row r="36">
@@ -6975,76 +6975,76 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>425.6565656565656</v>
+        <v>492.3847606029253</v>
       </c>
       <c r="C36" t="n">
-        <v>251.2035363754386</v>
+        <v>317.9317313217982</v>
       </c>
       <c r="D36" t="n">
-        <v>251.2035363754386</v>
+        <v>317.9317313217982</v>
       </c>
       <c r="E36" t="n">
-        <v>251.2035363754386</v>
+        <v>158.6942763163427</v>
       </c>
       <c r="F36" t="n">
-        <v>251.2035363754386</v>
+        <v>158.6942763163427</v>
       </c>
       <c r="G36" t="n">
-        <v>221.6228973880499</v>
+        <v>158.6942763163427</v>
       </c>
       <c r="H36" t="n">
-        <v>108.2537617956292</v>
+        <v>110.334904905842</v>
       </c>
       <c r="I36" t="n">
-        <v>17.95413265278571</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="J36" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K36" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L36" t="n">
-        <v>17.2</v>
+        <v>234.810827406191</v>
       </c>
       <c r="M36" t="n">
-        <v>182.2619638733197</v>
+        <v>473.4149733950735</v>
       </c>
       <c r="N36" t="n">
-        <v>395.1119638733197</v>
+        <v>712.019119383956</v>
       </c>
       <c r="O36" t="n">
-        <v>607.9619638733197</v>
+        <v>712.019119383956</v>
       </c>
       <c r="P36" t="n">
-        <v>790.6054414866707</v>
+        <v>894.6625969973069</v>
       </c>
       <c r="Q36" t="n">
-        <v>860</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R36" t="n">
-        <v>860</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S36" t="n">
-        <v>860</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T36" t="n">
-        <v>860</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U36" t="n">
-        <v>642.8282828282828</v>
+        <v>735.8335372470253</v>
       </c>
       <c r="V36" t="n">
-        <v>642.8282828282828</v>
+        <v>735.8335372470253</v>
       </c>
       <c r="W36" t="n">
-        <v>425.6565656565656</v>
+        <v>492.3847606029253</v>
       </c>
       <c r="X36" t="n">
-        <v>425.6565656565656</v>
+        <v>492.3847606029253</v>
       </c>
       <c r="Y36" t="n">
-        <v>425.6565656565656</v>
+        <v>492.3847606029253</v>
       </c>
     </row>
     <row r="37">
@@ -7054,76 +7054,76 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>17.2</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="C37" t="n">
-        <v>17.2</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="D37" t="n">
-        <v>17.2</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="E37" t="n">
-        <v>17.2</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="F37" t="n">
-        <v>17.2</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="G37" t="n">
-        <v>17.2</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="H37" t="n">
-        <v>17.2</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="I37" t="n">
-        <v>17.2</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="J37" t="n">
-        <v>17.2</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="K37" t="n">
-        <v>17.2</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="L37" t="n">
-        <v>44.51412500771298</v>
+        <v>856.8389900280785</v>
       </c>
       <c r="M37" t="n">
-        <v>83.70216319993516</v>
+        <v>896.0270282203006</v>
       </c>
       <c r="N37" t="n">
-        <v>127.3930138553715</v>
+        <v>939.7178788757369</v>
       </c>
       <c r="O37" t="n">
-        <v>151.7322904902707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="P37" t="n">
-        <v>151.7322904902707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q37" t="n">
-        <v>151.7322904902707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R37" t="n">
-        <v>151.7322904902707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S37" t="n">
-        <v>17.2</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T37" t="n">
-        <v>17.2</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U37" t="n">
-        <v>17.2</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="V37" t="n">
-        <v>17.2</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="W37" t="n">
-        <v>17.2</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="X37" t="n">
-        <v>17.2</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Y37" t="n">
-        <v>17.2</v>
+        <v>964.0571555106362</v>
       </c>
     </row>
     <row r="38">
@@ -7133,76 +7133,76 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>208.4848484848484</v>
+        <v>730.8505943024719</v>
       </c>
       <c r="C38" t="n">
-        <v>208.4848484848484</v>
+        <v>730.8505943024719</v>
       </c>
       <c r="D38" t="n">
-        <v>208.4848484848484</v>
+        <v>730.8505943024719</v>
       </c>
       <c r="E38" t="n">
-        <v>208.4848484848484</v>
+        <v>730.8505943024719</v>
       </c>
       <c r="F38" t="n">
-        <v>208.4848484848484</v>
+        <v>730.8505943024719</v>
       </c>
       <c r="G38" t="n">
-        <v>208.4848484848484</v>
+        <v>487.4018176583718</v>
       </c>
       <c r="H38" t="n">
-        <v>208.4848484848484</v>
+        <v>243.9530410142718</v>
       </c>
       <c r="I38" t="n">
-        <v>17.2</v>
+        <v>31.35113235729608</v>
       </c>
       <c r="J38" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K38" t="n">
-        <v>120.2150059109224</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L38" t="n">
-        <v>300.290857495581</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M38" t="n">
-        <v>513.1408574955809</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N38" t="n">
-        <v>718.9953797028202</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O38" t="n">
-        <v>860</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P38" t="n">
-        <v>860</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q38" t="n">
-        <v>860</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="R38" t="n">
-        <v>860</v>
+        <v>802.5825927271064</v>
       </c>
       <c r="S38" t="n">
-        <v>860</v>
+        <v>730.8505943024719</v>
       </c>
       <c r="T38" t="n">
-        <v>642.8282828282828</v>
+        <v>730.8505943024719</v>
       </c>
       <c r="U38" t="n">
-        <v>425.6565656565656</v>
+        <v>730.8505943024719</v>
       </c>
       <c r="V38" t="n">
-        <v>425.6565656565656</v>
+        <v>730.8505943024719</v>
       </c>
       <c r="W38" t="n">
-        <v>425.6565656565656</v>
+        <v>730.8505943024719</v>
       </c>
       <c r="X38" t="n">
-        <v>425.6565656565656</v>
+        <v>730.8505943024719</v>
       </c>
       <c r="Y38" t="n">
-        <v>208.4848484848484</v>
+        <v>730.8505943024719</v>
       </c>
     </row>
     <row r="39">
@@ -7212,76 +7212,76 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>657.813405358766</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C39" t="n">
-        <v>483.360376077639</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D39" t="n">
-        <v>334.4259664163877</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E39" t="n">
-        <v>175.1885114109322</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F39" t="n">
-        <v>28.65395343781719</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G39" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H39" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I39" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J39" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K39" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L39" t="n">
-        <v>230.05</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="M39" t="n">
-        <v>442.9</v>
+        <v>257.8852890990952</v>
       </c>
       <c r="N39" t="n">
-        <v>655.75</v>
+        <v>473.4149733950735</v>
       </c>
       <c r="O39" t="n">
-        <v>860</v>
+        <v>712.019119383956</v>
       </c>
       <c r="P39" t="n">
-        <v>860</v>
+        <v>894.6625969973069</v>
       </c>
       <c r="Q39" t="n">
-        <v>860</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R39" t="n">
-        <v>860</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S39" t="n">
-        <v>860</v>
+        <v>790.6398109613051</v>
       </c>
       <c r="T39" t="n">
-        <v>657.813405358766</v>
+        <v>690.5083698110992</v>
       </c>
       <c r="U39" t="n">
-        <v>657.813405358766</v>
+        <v>462.2847515474883</v>
       </c>
       <c r="V39" t="n">
-        <v>657.813405358766</v>
+        <v>227.1326433157456</v>
       </c>
       <c r="W39" t="n">
-        <v>657.813405358766</v>
+        <v>227.1326433157456</v>
       </c>
       <c r="X39" t="n">
-        <v>657.813405358766</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="Y39" t="n">
-        <v>657.813405358766</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
     <row r="40">
@@ -7291,76 +7291,76 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>17.2</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="C40" t="n">
-        <v>17.2</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="D40" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E40" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F40" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G40" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H40" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I40" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J40" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K40" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L40" t="n">
-        <v>44.51412500771298</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M40" t="n">
-        <v>83.70216319993516</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N40" t="n">
-        <v>127.3930138553715</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O40" t="n">
-        <v>151.7322904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P40" t="n">
-        <v>151.7322904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Q40" t="n">
-        <v>151.7322904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="R40" t="n">
-        <v>151.7322904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="S40" t="n">
-        <v>151.7322904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="T40" t="n">
-        <v>151.7322904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="U40" t="n">
-        <v>17.2</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="V40" t="n">
-        <v>17.2</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="W40" t="n">
-        <v>17.2</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="X40" t="n">
-        <v>17.2</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Y40" t="n">
-        <v>17.2</v>
+        <v>153.8134336004835</v>
       </c>
     </row>
     <row r="41">
@@ -7370,76 +7370,76 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>232.1915151515151</v>
+        <v>448.2340696092722</v>
       </c>
       <c r="C41" t="n">
-        <v>232.1915151515151</v>
+        <v>448.2340696092722</v>
       </c>
       <c r="D41" t="n">
-        <v>232.1915151515151</v>
+        <v>232.6540053493298</v>
       </c>
       <c r="E41" t="n">
-        <v>17.04</v>
+        <v>232.6540053493298</v>
       </c>
       <c r="F41" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="G41" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="H41" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="I41" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="J41" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="K41" t="n">
-        <v>120.0550059109223</v>
+        <v>17.62165426160527</v>
       </c>
       <c r="L41" t="n">
-        <v>300.1308574955809</v>
+        <v>197.6975058462639</v>
       </c>
       <c r="M41" t="n">
-        <v>511.0008574955809</v>
+        <v>408.9875268274333</v>
       </c>
       <c r="N41" t="n">
-        <v>716.8553797028203</v>
+        <v>614.8420490346726</v>
       </c>
       <c r="O41" t="n">
-        <v>852</v>
+        <v>764.0369991773207</v>
       </c>
       <c r="P41" t="n">
-        <v>852</v>
+        <v>853.6970544693717</v>
       </c>
       <c r="Q41" t="n">
-        <v>852</v>
+        <v>843.6054391011446</v>
       </c>
       <c r="R41" t="n">
-        <v>852</v>
+        <v>843.6054391011446</v>
       </c>
       <c r="S41" t="n">
-        <v>852</v>
+        <v>843.6054391011446</v>
       </c>
       <c r="T41" t="n">
-        <v>852</v>
+        <v>663.8141338692145</v>
       </c>
       <c r="U41" t="n">
-        <v>662.4945454545455</v>
+        <v>663.8141338692145</v>
       </c>
       <c r="V41" t="n">
-        <v>447.3430303030303</v>
+        <v>448.2340696092722</v>
       </c>
       <c r="W41" t="n">
-        <v>232.1915151515151</v>
+        <v>448.2340696092722</v>
       </c>
       <c r="X41" t="n">
-        <v>232.1915151515151</v>
+        <v>448.2340696092722</v>
       </c>
       <c r="Y41" t="n">
-        <v>232.1915151515151</v>
+        <v>448.2340696092722</v>
       </c>
     </row>
     <row r="42">
@@ -7449,76 +7449,76 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>636.8484848484849</v>
+        <v>222.5051912389426</v>
       </c>
       <c r="C42" t="n">
-        <v>636.8484848484849</v>
+        <v>222.5051912389426</v>
       </c>
       <c r="D42" t="n">
-        <v>487.9140751872336</v>
+        <v>222.5051912389426</v>
       </c>
       <c r="E42" t="n">
-        <v>415.6745189829202</v>
+        <v>155.8047665067719</v>
       </c>
       <c r="F42" t="n">
-        <v>269.1399610098052</v>
+        <v>155.8047665067719</v>
       </c>
       <c r="G42" t="n">
-        <v>130.4091355924207</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="H42" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="I42" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="J42" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="K42" t="n">
-        <v>142.3975600578374</v>
+        <v>142.4315011472248</v>
       </c>
       <c r="L42" t="n">
-        <v>353.2675600578374</v>
+        <v>353.7215221283943</v>
       </c>
       <c r="M42" t="n">
-        <v>564.1375600578374</v>
+        <v>565.0115431095638</v>
       </c>
       <c r="N42" t="n">
-        <v>641.13</v>
+        <v>776.3015640907333</v>
       </c>
       <c r="O42" t="n">
-        <v>852</v>
+        <v>784.3024959560423</v>
       </c>
       <c r="P42" t="n">
-        <v>852</v>
+        <v>784.3024959560423</v>
       </c>
       <c r="Q42" t="n">
-        <v>852</v>
+        <v>853.6970544693717</v>
       </c>
       <c r="R42" t="n">
-        <v>852</v>
+        <v>853.6970544693717</v>
       </c>
       <c r="S42" t="n">
-        <v>852</v>
+        <v>853.6970544693717</v>
       </c>
       <c r="T42" t="n">
-        <v>852</v>
+        <v>853.6970544693717</v>
       </c>
       <c r="U42" t="n">
-        <v>852</v>
+        <v>638.1169902094293</v>
       </c>
       <c r="V42" t="n">
-        <v>852</v>
+        <v>638.1169902094293</v>
       </c>
       <c r="W42" t="n">
-        <v>636.8484848484849</v>
+        <v>638.1169902094293</v>
       </c>
       <c r="X42" t="n">
-        <v>636.8484848484849</v>
+        <v>430.2654900038965</v>
       </c>
       <c r="Y42" t="n">
-        <v>636.8484848484849</v>
+        <v>222.5051912389426</v>
       </c>
     </row>
     <row r="43">
@@ -7528,76 +7528,76 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>717.4677095097293</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="C43" t="n">
-        <v>717.4677095097293</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="D43" t="n">
-        <v>717.4677095097293</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="E43" t="n">
-        <v>717.4677095097293</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="F43" t="n">
-        <v>717.4677095097293</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="G43" t="n">
-        <v>717.4677095097293</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="H43" t="n">
-        <v>717.4677095097293</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="I43" t="n">
-        <v>717.4677095097293</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="J43" t="n">
-        <v>717.4677095097293</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="K43" t="n">
-        <v>717.4677095097293</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="L43" t="n">
-        <v>744.7818345174422</v>
+        <v>44.38806609710041</v>
       </c>
       <c r="M43" t="n">
-        <v>783.9698727096644</v>
+        <v>83.57610428932259</v>
       </c>
       <c r="N43" t="n">
-        <v>827.6607233651007</v>
+        <v>127.2669549447589</v>
       </c>
       <c r="O43" t="n">
-        <v>852</v>
+        <v>151.6062315796582</v>
       </c>
       <c r="P43" t="n">
-        <v>852</v>
+        <v>151.6062315796582</v>
       </c>
       <c r="Q43" t="n">
-        <v>852</v>
+        <v>151.6062315796582</v>
       </c>
       <c r="R43" t="n">
-        <v>852</v>
+        <v>151.6062315796582</v>
       </c>
       <c r="S43" t="n">
-        <v>852</v>
+        <v>151.6062315796582</v>
       </c>
       <c r="T43" t="n">
-        <v>852</v>
+        <v>151.6062315796582</v>
       </c>
       <c r="U43" t="n">
-        <v>852</v>
+        <v>151.6062315796582</v>
       </c>
       <c r="V43" t="n">
-        <v>852</v>
+        <v>151.6062315796582</v>
       </c>
       <c r="W43" t="n">
-        <v>852</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="X43" t="n">
-        <v>852</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="Y43" t="n">
-        <v>717.4677095097293</v>
+        <v>17.07394108938743</v>
       </c>
     </row>
     <row r="44">
@@ -8436,16 +8436,16 @@
         <v>220.0898510449805</v>
       </c>
       <c r="L8" t="n">
-        <v>261.7664149699872</v>
+        <v>235.7664149699872</v>
       </c>
       <c r="M8" t="n">
-        <v>255.2957281767677</v>
+        <v>230.3462332272727</v>
       </c>
       <c r="N8" t="n">
-        <v>255.4130635965909</v>
+        <v>229.4130635965909</v>
       </c>
       <c r="O8" t="n">
-        <v>256.0982114216868</v>
+        <v>230.0982114216867</v>
       </c>
       <c r="P8" t="n">
         <v>231.2329957552695</v>
@@ -8515,19 +8515,19 @@
         <v>137.841438974359</v>
       </c>
       <c r="L9" t="n">
-        <v>164.5543797798742</v>
+        <v>138.5543797798742</v>
       </c>
       <c r="M9" t="n">
-        <v>168.1340339220183</v>
+        <v>142.1340339220183</v>
       </c>
       <c r="N9" t="n">
-        <v>156.2912070328283</v>
+        <v>131.3417120833333</v>
       </c>
       <c r="O9" t="n">
         <v>142.5962444444444</v>
       </c>
       <c r="P9" t="n">
-        <v>159.9744074143302</v>
+        <v>133.9744074143302</v>
       </c>
       <c r="Q9" t="n">
         <v>139.9817740860215</v>
@@ -8594,16 +8594,16 @@
         <v>106.7437663446525</v>
       </c>
       <c r="L10" t="n">
-        <v>160.8846762812383</v>
+        <v>134.8846762812383</v>
       </c>
       <c r="M10" t="n">
-        <v>164.9257839476051</v>
+        <v>138.9257839476051</v>
       </c>
       <c r="N10" t="n">
-        <v>153.6855444652332</v>
+        <v>127.6855444652332</v>
       </c>
       <c r="O10" t="n">
-        <v>163.0416663658825</v>
+        <v>138.4565384518428</v>
       </c>
       <c r="P10" t="n">
         <v>135.0065633140411</v>
@@ -8673,19 +8673,19 @@
         <v>220.0898510449805</v>
       </c>
       <c r="L11" t="n">
-        <v>260.7159099194822</v>
+        <v>235.7664149699872</v>
       </c>
       <c r="M11" t="n">
-        <v>256.3462332272727</v>
+        <v>230.3462332272727</v>
       </c>
       <c r="N11" t="n">
-        <v>255.4130635965909</v>
+        <v>229.4130635965909</v>
       </c>
       <c r="O11" t="n">
         <v>230.0982114216867</v>
       </c>
       <c r="P11" t="n">
-        <v>257.2329957552695</v>
+        <v>231.2329957552695</v>
       </c>
       <c r="Q11" t="n">
         <v>212.3149906599047</v>
@@ -8752,10 +8752,10 @@
         <v>137.841438974359</v>
       </c>
       <c r="L12" t="n">
-        <v>164.5543797798742</v>
+        <v>138.5543797798742</v>
       </c>
       <c r="M12" t="n">
-        <v>168.1340339220183</v>
+        <v>142.1340339220183</v>
       </c>
       <c r="N12" t="n">
         <v>131.3417120833333</v>
@@ -8764,10 +8764,10 @@
         <v>142.5962444444444</v>
       </c>
       <c r="P12" t="n">
-        <v>158.9239023638252</v>
+        <v>133.9744074143302</v>
       </c>
       <c r="Q12" t="n">
-        <v>165.9817740860215</v>
+        <v>139.9817740860215</v>
       </c>
       <c r="R12" t="n">
         <v>45.52166981132082</v>
@@ -8831,16 +8831,16 @@
         <v>106.7437663446525</v>
       </c>
       <c r="L13" t="n">
-        <v>160.8846762812383</v>
+        <v>134.8846762812383</v>
       </c>
       <c r="M13" t="n">
-        <v>164.9257839476051</v>
+        <v>138.9257839476051</v>
       </c>
       <c r="N13" t="n">
-        <v>153.6855444652332</v>
+        <v>127.6855444652332</v>
       </c>
       <c r="O13" t="n">
-        <v>163.0416663658825</v>
+        <v>138.4565384518428</v>
       </c>
       <c r="P13" t="n">
         <v>135.0065633140411</v>
@@ -8907,10 +8907,10 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K14" t="n">
-        <v>246.0898510449805</v>
+        <v>220.0898510449805</v>
       </c>
       <c r="L14" t="n">
-        <v>261.7664149699872</v>
+        <v>235.7664149699872</v>
       </c>
       <c r="M14" t="n">
         <v>230.3462332272727</v>
@@ -8919,10 +8919,10 @@
         <v>229.4130635965909</v>
       </c>
       <c r="O14" t="n">
-        <v>255.0477063711817</v>
+        <v>230.0982114216867</v>
       </c>
       <c r="P14" t="n">
-        <v>257.2329957552695</v>
+        <v>231.2329957552695</v>
       </c>
       <c r="Q14" t="n">
         <v>212.3149906599047</v>
@@ -8992,19 +8992,19 @@
         <v>138.5543797798742</v>
       </c>
       <c r="M15" t="n">
-        <v>167.0835288715133</v>
+        <v>142.1340339220183</v>
       </c>
       <c r="N15" t="n">
         <v>131.3417120833333</v>
       </c>
       <c r="O15" t="n">
-        <v>168.5962444444444</v>
+        <v>142.5962444444444</v>
       </c>
       <c r="P15" t="n">
-        <v>159.9744074143302</v>
+        <v>133.9744074143302</v>
       </c>
       <c r="Q15" t="n">
-        <v>165.9817740860215</v>
+        <v>139.9817740860215</v>
       </c>
       <c r="R15" t="n">
         <v>45.52166981132082</v>
@@ -9068,16 +9068,16 @@
         <v>106.7437663446525</v>
       </c>
       <c r="L16" t="n">
-        <v>160.8846762812383</v>
+        <v>134.8846762812383</v>
       </c>
       <c r="M16" t="n">
-        <v>164.9257839476051</v>
+        <v>138.9257839476051</v>
       </c>
       <c r="N16" t="n">
-        <v>153.6855444652332</v>
+        <v>127.6855444652332</v>
       </c>
       <c r="O16" t="n">
-        <v>163.0416663658825</v>
+        <v>138.4565384518428</v>
       </c>
       <c r="P16" t="n">
         <v>135.0065633140411</v>
@@ -9144,22 +9144,22 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K17" t="n">
-        <v>220.0898510449805</v>
+        <v>246.5651278099304</v>
       </c>
       <c r="L17" t="n">
         <v>235.7664149699872</v>
       </c>
       <c r="M17" t="n">
-        <v>257.2149200959596</v>
+        <v>257.9362584875889</v>
       </c>
       <c r="N17" t="n">
-        <v>257.4130635965909</v>
+        <v>257.0030888569071</v>
       </c>
       <c r="O17" t="n">
-        <v>258.0982114216868</v>
+        <v>257.6882366820029</v>
       </c>
       <c r="P17" t="n">
-        <v>259.2329957552695</v>
+        <v>231.2329957552695</v>
       </c>
       <c r="Q17" t="n">
         <v>212.3149906599047</v>
@@ -9226,22 +9226,22 @@
         <v>137.841438974359</v>
       </c>
       <c r="L18" t="n">
-        <v>138.5543797798742</v>
+        <v>165.029656544824</v>
       </c>
       <c r="M18" t="n">
         <v>142.1340339220183</v>
       </c>
       <c r="N18" t="n">
-        <v>158.2103989520202</v>
+        <v>158.9317373436494</v>
       </c>
       <c r="O18" t="n">
-        <v>170.5962444444444</v>
+        <v>170.1862697047606</v>
       </c>
       <c r="P18" t="n">
-        <v>161.9744074143302</v>
+        <v>161.5644326746464</v>
       </c>
       <c r="Q18" t="n">
-        <v>167.9817740860215</v>
+        <v>139.9817740860215</v>
       </c>
       <c r="R18" t="n">
         <v>45.52166981132082</v>
@@ -9308,10 +9308,10 @@
         <v>162.4747015415544</v>
       </c>
       <c r="M19" t="n">
-        <v>166.9257839476051</v>
+        <v>166.5158092079212</v>
       </c>
       <c r="N19" t="n">
-        <v>155.6855444652332</v>
+        <v>155.2755697255493</v>
       </c>
       <c r="O19" t="n">
         <v>163.0416663658825</v>
@@ -9396,7 +9396,7 @@
         <v>380.8001812627454</v>
       </c>
       <c r="P20" t="n">
-        <v>321.7421299892367</v>
+        <v>321.7987081714826</v>
       </c>
       <c r="Q20" t="n">
         <v>212.3149906599047</v>
@@ -9463,22 +9463,22 @@
         <v>264.4652370125786</v>
       </c>
       <c r="L21" t="n">
-        <v>370.8403453034592</v>
+        <v>138.5543797798742</v>
       </c>
       <c r="M21" t="n">
-        <v>383.1340339220183</v>
+        <v>233.2169876979182</v>
       </c>
       <c r="N21" t="n">
-        <v>372.3417120833333</v>
+        <v>372.3560009609923</v>
       </c>
       <c r="O21" t="n">
-        <v>255.9491071452661</v>
+        <v>383.6105333221035</v>
       </c>
       <c r="P21" t="n">
-        <v>133.9744074143302</v>
+        <v>318.4627686399372</v>
       </c>
       <c r="Q21" t="n">
-        <v>139.9817740860215</v>
+        <v>210.0772877358491</v>
       </c>
       <c r="R21" t="n">
         <v>45.52166981132082</v>
@@ -9618,7 +9618,7 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K23" t="n">
-        <v>324.0888343889188</v>
+        <v>324.1454125711647</v>
       </c>
       <c r="L23" t="n">
         <v>417.6612145504504</v>
@@ -9697,22 +9697,22 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K24" t="n">
-        <v>264.4652370125786</v>
+        <v>137.841438974359</v>
       </c>
       <c r="L24" t="n">
-        <v>173.0976943544532</v>
+        <v>138.5543797798742</v>
       </c>
       <c r="M24" t="n">
-        <v>383.1340339220183</v>
+        <v>383.1483227996774</v>
       </c>
       <c r="N24" t="n">
-        <v>372.3417120833333</v>
+        <v>349.0484638974528</v>
       </c>
       <c r="O24" t="n">
-        <v>383.5962444444444</v>
+        <v>383.6105333221035</v>
       </c>
       <c r="P24" t="n">
-        <v>133.9744074143302</v>
+        <v>318.4627686399372</v>
       </c>
       <c r="Q24" t="n">
         <v>210.0772877358491</v>
@@ -9870,7 +9870,7 @@
         <v>380.8001812627454</v>
       </c>
       <c r="P26" t="n">
-        <v>321.7421299892367</v>
+        <v>321.7987081714826</v>
       </c>
       <c r="Q26" t="n">
         <v>212.3149906599047</v>
@@ -9934,25 +9934,25 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K27" t="n">
-        <v>264.4652370125786</v>
+        <v>137.841438974359</v>
       </c>
       <c r="L27" t="n">
         <v>138.5543797798742</v>
       </c>
       <c r="M27" t="n">
-        <v>383.1340339220183</v>
+        <v>383.1483227996774</v>
       </c>
       <c r="N27" t="n">
-        <v>372.3417120833333</v>
+        <v>372.3560009609923</v>
       </c>
       <c r="O27" t="n">
-        <v>303.7467114432442</v>
+        <v>360.302996258564</v>
       </c>
       <c r="P27" t="n">
         <v>318.4627686399372</v>
       </c>
       <c r="Q27" t="n">
-        <v>139.9817740860215</v>
+        <v>210.0772877358491</v>
       </c>
       <c r="R27" t="n">
         <v>45.52166981132082</v>
@@ -10101,7 +10101,7 @@
         <v>449.5135334928325</v>
       </c>
       <c r="N29" t="n">
-        <v>437.2903462297383</v>
+        <v>437.3469244119842</v>
       </c>
       <c r="O29" t="n">
         <v>380.8001812627454</v>
@@ -10174,16 +10174,16 @@
         <v>137.841438974359</v>
       </c>
       <c r="L30" t="n">
-        <v>356.2331311670658</v>
+        <v>138.5543797798742</v>
       </c>
       <c r="M30" t="n">
-        <v>142.1340339220183</v>
+        <v>383.1483227996774</v>
       </c>
       <c r="N30" t="n">
-        <v>372.3417120833333</v>
+        <v>372.3560009609923</v>
       </c>
       <c r="O30" t="n">
-        <v>383.5962444444444</v>
+        <v>360.302996258564</v>
       </c>
       <c r="P30" t="n">
         <v>318.4627686399372</v>
@@ -10332,10 +10332,10 @@
         <v>324.1454125711647</v>
       </c>
       <c r="L32" t="n">
-        <v>318.8224416842694</v>
+        <v>417.6612145504504</v>
       </c>
       <c r="M32" t="n">
-        <v>445.3462332272727</v>
+        <v>449.5135334928325</v>
       </c>
       <c r="N32" t="n">
         <v>437.3469244119842</v>
@@ -10411,16 +10411,16 @@
         <v>264.4652370125786</v>
       </c>
       <c r="L33" t="n">
-        <v>138.5543797798742</v>
+        <v>229.6373335557741</v>
       </c>
       <c r="M33" t="n">
-        <v>357.1340339220183</v>
+        <v>383.1483227996774</v>
       </c>
       <c r="N33" t="n">
-        <v>171.4471704828104</v>
+        <v>372.3560009609923</v>
       </c>
       <c r="O33" t="n">
-        <v>357.5962444444444</v>
+        <v>142.5962444444444</v>
       </c>
       <c r="P33" t="n">
         <v>318.4627686399372</v>
@@ -10572,13 +10572,13 @@
         <v>417.6612145504504</v>
       </c>
       <c r="M35" t="n">
-        <v>445.3462332272727</v>
+        <v>449.5135334928325</v>
       </c>
       <c r="N35" t="n">
         <v>437.3469244119842</v>
       </c>
       <c r="O35" t="n">
-        <v>281.9614083965644</v>
+        <v>380.8001812627454</v>
       </c>
       <c r="P35" t="n">
         <v>321.7987081714826</v>
@@ -10648,16 +10648,16 @@
         <v>137.841438974359</v>
       </c>
       <c r="L36" t="n">
-        <v>138.5543797798742</v>
+        <v>356.2611315939937</v>
       </c>
       <c r="M36" t="n">
-        <v>308.8632903597151</v>
+        <v>383.1483227996774</v>
       </c>
       <c r="N36" t="n">
-        <v>346.3417120833333</v>
+        <v>372.3560009609923</v>
       </c>
       <c r="O36" t="n">
-        <v>357.5962444444444</v>
+        <v>142.5962444444444</v>
       </c>
       <c r="P36" t="n">
         <v>318.4627686399372</v>
@@ -10809,16 +10809,16 @@
         <v>417.6612145504504</v>
       </c>
       <c r="M38" t="n">
-        <v>445.3462332272727</v>
+        <v>449.5135334928325</v>
       </c>
       <c r="N38" t="n">
         <v>437.3469244119842</v>
       </c>
       <c r="O38" t="n">
-        <v>372.5271208127775</v>
+        <v>380.8001812627454</v>
       </c>
       <c r="P38" t="n">
-        <v>231.2329957552695</v>
+        <v>321.7987081714826</v>
       </c>
       <c r="Q38" t="n">
         <v>212.3149906599047</v>
@@ -10885,22 +10885,22 @@
         <v>137.841438974359</v>
       </c>
       <c r="L39" t="n">
-        <v>353.5543797798742</v>
+        <v>138.5543797798742</v>
       </c>
       <c r="M39" t="n">
-        <v>357.1340339220183</v>
+        <v>383.1483227996774</v>
       </c>
       <c r="N39" t="n">
-        <v>346.3417120833333</v>
+        <v>349.0484638974528</v>
       </c>
       <c r="O39" t="n">
-        <v>348.9093757575757</v>
+        <v>383.6105333221035</v>
       </c>
       <c r="P39" t="n">
-        <v>133.9744074143302</v>
+        <v>318.4627686399372</v>
       </c>
       <c r="Q39" t="n">
-        <v>139.9817740860215</v>
+        <v>210.0772877358491</v>
       </c>
       <c r="R39" t="n">
         <v>45.52166981132082</v>
@@ -11040,22 +11040,22 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K41" t="n">
-        <v>324.1454125711647</v>
+        <v>220.6430966734834</v>
       </c>
       <c r="L41" t="n">
         <v>417.6612145504504</v>
       </c>
       <c r="M41" t="n">
-        <v>443.3462332272727</v>
+        <v>443.7704968446156</v>
       </c>
       <c r="N41" t="n">
         <v>437.3469244119842</v>
       </c>
       <c r="O41" t="n">
-        <v>366.6079288935854</v>
+        <v>380.8001812627454</v>
       </c>
       <c r="P41" t="n">
-        <v>231.2329957552695</v>
+        <v>321.7987081714826</v>
       </c>
       <c r="Q41" t="n">
         <v>212.3149906599047</v>
@@ -11122,22 +11122,22 @@
         <v>264.4652370125786</v>
       </c>
       <c r="L42" t="n">
-        <v>351.5543797798742</v>
+        <v>351.9786433972171</v>
       </c>
       <c r="M42" t="n">
-        <v>355.1340339220183</v>
+        <v>355.5582975393612</v>
       </c>
       <c r="N42" t="n">
-        <v>209.1118534390531</v>
+        <v>344.7659757006762</v>
       </c>
       <c r="O42" t="n">
-        <v>355.5962444444444</v>
+        <v>150.6779938033424</v>
       </c>
       <c r="P42" t="n">
         <v>133.9744074143302</v>
       </c>
       <c r="Q42" t="n">
-        <v>139.9817740860215</v>
+        <v>210.0772877358491</v>
       </c>
       <c r="R42" t="n">
         <v>45.52166981132082</v>
@@ -22993,16 +22993,16 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G8" t="n">
-        <v>414.3419260842924</v>
+        <v>415.302737515135</v>
       </c>
       <c r="H8" t="n">
-        <v>313.4748021157671</v>
+        <v>339.4748021157671</v>
       </c>
       <c r="I8" t="n">
-        <v>184.4758895704059</v>
+        <v>210.4758895704059</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -23023,10 +23023,10 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R8" t="n">
-        <v>123.8691179411497</v>
+        <v>149.8691179411497</v>
       </c>
       <c r="S8" t="n">
         <v>209.0200695862453</v>
@@ -23075,13 +23075,13 @@
         <v>137.3435171632106</v>
       </c>
       <c r="H9" t="n">
-        <v>90.08123556275433</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="I9" t="n">
-        <v>63.39663285141508</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>0.7465913262578567</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -23105,10 +23105,10 @@
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>74.15783415264313</v>
+        <v>100.1578341526431</v>
       </c>
       <c r="S9" t="n">
-        <v>145.6831711038378</v>
+        <v>171.6831711038378</v>
       </c>
       <c r="T9" t="n">
         <v>200.1647286948216</v>
@@ -23178,19 +23178,19 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>2.721440735106512</v>
       </c>
       <c r="Q10" t="n">
-        <v>60.16204325169439</v>
+        <v>86.16204325169439</v>
       </c>
       <c r="R10" t="n">
-        <v>151.2933913771695</v>
+        <v>177.2933913771695</v>
       </c>
       <c r="S10" t="n">
-        <v>198.0165980369723</v>
+        <v>224.0165980369723</v>
       </c>
       <c r="T10" t="n">
-        <v>208.1233462948377</v>
+        <v>227.9455894282815</v>
       </c>
       <c r="U10" t="n">
         <v>286.3190293564909</v>
@@ -23260,19 +23260,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R11" t="n">
-        <v>123.8691179411497</v>
+        <v>149.8691179411497</v>
       </c>
       <c r="S11" t="n">
-        <v>183.0200695862453</v>
+        <v>209.0200695862453</v>
       </c>
       <c r="T11" t="n">
-        <v>197.0958495641314</v>
+        <v>223.0958495641314</v>
       </c>
       <c r="U11" t="n">
-        <v>238.4355521223813</v>
+        <v>251.3456529078365</v>
       </c>
       <c r="V11" t="n">
         <v>327.7522584701349</v>
@@ -23306,16 +23306,16 @@
         <v>157.6450804554009</v>
       </c>
       <c r="F12" t="n">
-        <v>122.1684123933839</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="G12" t="n">
-        <v>111.3435171632106</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H12" t="n">
-        <v>86.23544423649646</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="I12" t="n">
-        <v>63.39663285141508</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="J12" t="n">
         <v>0.7465913262578567</v>
@@ -23397,10 +23397,10 @@
         <v>155.4504749272583</v>
       </c>
       <c r="J13" t="n">
-        <v>67.35918011667277</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>22.26949182588285</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -23424,13 +23424,13 @@
         <v>177.2933913771695</v>
       </c>
       <c r="S13" t="n">
-        <v>198.0165980369723</v>
+        <v>224.0165980369723</v>
       </c>
       <c r="T13" t="n">
-        <v>201.9455894282815</v>
+        <v>227.9455894282815</v>
       </c>
       <c r="U13" t="n">
-        <v>286.0448373138235</v>
+        <v>286.3190293564909</v>
       </c>
       <c r="V13" t="n">
         <v>252.137643323828</v>
@@ -23452,7 +23452,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>356.7338416634806</v>
+        <v>382.7338416634806</v>
       </c>
       <c r="C14" t="n">
         <v>365.2728917710076</v>
@@ -23464,7 +23464,7 @@
         <v>381.9303700722618</v>
       </c>
       <c r="F14" t="n">
-        <v>380.8760457417114</v>
+        <v>406.8760457417114</v>
       </c>
       <c r="G14" t="n">
         <v>415.302737515135</v>
@@ -23506,7 +23506,7 @@
         <v>209.0200695862453</v>
       </c>
       <c r="T14" t="n">
-        <v>200.1950495641314</v>
+        <v>223.0958495641314</v>
       </c>
       <c r="U14" t="n">
         <v>251.3456529078365</v>
@@ -23521,7 +23521,7 @@
         <v>369.731100678469</v>
       </c>
       <c r="Y14" t="n">
-        <v>360.2379386560536</v>
+        <v>386.2379386560536</v>
       </c>
     </row>
     <row r="15">
@@ -23543,19 +23543,19 @@
         <v>157.6450804554009</v>
       </c>
       <c r="F15" t="n">
-        <v>122.9150037196417</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="G15" t="n">
-        <v>111.3435171632106</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H15" t="n">
-        <v>86.23544423649646</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="I15" t="n">
-        <v>63.39663285141508</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>0.7465913262578567</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
@@ -23637,7 +23637,7 @@
         <v>93.35918011667277</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>22.26949182588285</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -23652,16 +23652,16 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>2.447248692439088</v>
+        <v>2.721440735106512</v>
       </c>
       <c r="Q16" t="n">
-        <v>60.16204325169439</v>
+        <v>86.16204325169439</v>
       </c>
       <c r="R16" t="n">
-        <v>151.2933913771695</v>
+        <v>177.2933913771695</v>
       </c>
       <c r="S16" t="n">
-        <v>198.0165980369723</v>
+        <v>224.0165980369723</v>
       </c>
       <c r="T16" t="n">
         <v>227.9455894282815</v>
@@ -23734,25 +23734,25 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>9.990699214544804</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>149.8691179411497</v>
+        <v>122.2790926808335</v>
       </c>
       <c r="S17" t="n">
-        <v>209.0200695862453</v>
+        <v>181.4300443259292</v>
       </c>
       <c r="T17" t="n">
-        <v>198.4334495641314</v>
+        <v>195.5058243038152</v>
       </c>
       <c r="U17" t="n">
-        <v>223.3456529078365</v>
+        <v>237.0350578730948</v>
       </c>
       <c r="V17" t="n">
-        <v>299.7522584701349</v>
+        <v>327.7522584701349</v>
       </c>
       <c r="W17" t="n">
-        <v>321.240968717413</v>
+        <v>349.240968717413</v>
       </c>
       <c r="X17" t="n">
         <v>369.731100678469</v>
@@ -23786,13 +23786,13 @@
         <v>137.3435171632106</v>
       </c>
       <c r="H18" t="n">
-        <v>112.2354442364965</v>
+        <v>84.64541897618032</v>
       </c>
       <c r="I18" t="n">
-        <v>89.39663285141508</v>
+        <v>61.80660759109894</v>
       </c>
       <c r="J18" t="n">
-        <v>0.7465913262578567</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
@@ -23816,16 +23816,16 @@
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>72.15783415264313</v>
+        <v>72.56780889232699</v>
       </c>
       <c r="S18" t="n">
-        <v>143.6831711038378</v>
+        <v>148.1284681808092</v>
       </c>
       <c r="T18" t="n">
-        <v>172.1647286948216</v>
+        <v>200.1647286948216</v>
       </c>
       <c r="U18" t="n">
-        <v>201.2789820809748</v>
+        <v>225.9413820809748</v>
       </c>
       <c r="V18" t="n">
         <v>232.8005871494253</v>
@@ -23892,16 +23892,16 @@
         <v>2.721440735106512</v>
       </c>
       <c r="Q19" t="n">
-        <v>58.16204325169439</v>
+        <v>58.57201799137825</v>
       </c>
       <c r="R19" t="n">
-        <v>149.2933913771695</v>
+        <v>149.7033661168533</v>
       </c>
       <c r="S19" t="n">
-        <v>196.0165980369723</v>
+        <v>196.4265727766561</v>
       </c>
       <c r="T19" t="n">
-        <v>205.9231218020954</v>
+        <v>227.9455894282815</v>
       </c>
       <c r="U19" t="n">
         <v>286.3190293564909</v>
@@ -23910,7 +23910,7 @@
         <v>252.137643323828</v>
       </c>
       <c r="W19" t="n">
-        <v>286.522998336591</v>
+        <v>264.0742389760816</v>
       </c>
       <c r="X19" t="n">
         <v>225.7096553890372</v>
@@ -23929,7 +23929,7 @@
         <v>382.7338416634806</v>
       </c>
       <c r="C20" t="n">
-        <v>124.2728917710076</v>
+        <v>365.2728917710076</v>
       </c>
       <c r="D20" t="n">
         <v>354.683041620683</v>
@@ -23941,10 +23941,10 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G20" t="n">
-        <v>415.302737515135</v>
+        <v>174.288448637476</v>
       </c>
       <c r="H20" t="n">
-        <v>309.7337994057071</v>
+        <v>236.4659043839653</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
@@ -23974,13 +23974,13 @@
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>149.8691179411497</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>223.0958495641314</v>
       </c>
       <c r="U20" t="n">
         <v>251.3456529078365</v>
@@ -24014,22 +24014,22 @@
         <v>147.4450655646388</v>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>157.6450804554009</v>
       </c>
       <c r="F21" t="n">
         <v>145.0692123933839</v>
       </c>
       <c r="G21" t="n">
-        <v>39.61816706656634</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>7.497060989136827</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>0.7465913262578567</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
@@ -24053,19 +24053,19 @@
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>100.1578341526431</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>200.1647286948216</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>225.9413820809748</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>232.8005871494253</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
         <v>251.6949831609196</v>
@@ -24074,7 +24074,7 @@
         <v>205.7729852034775</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>205.6826957773044</v>
       </c>
     </row>
     <row r="22">
@@ -24084,7 +24084,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>46.64501259656927</v>
+        <v>179.8319801819373</v>
       </c>
       <c r="C22" t="n">
         <v>167.2468210986278</v>
@@ -24129,10 +24129,10 @@
         <v>2.721440735106512</v>
       </c>
       <c r="Q22" t="n">
-        <v>86.16204325169439</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>177.2933913771695</v>
+        <v>130.2684670434958</v>
       </c>
       <c r="S22" t="n">
         <v>224.0165980369723</v>
@@ -24172,7 +24172,7 @@
         <v>354.683041620683</v>
       </c>
       <c r="E23" t="n">
-        <v>140.9303700722618</v>
+        <v>140.9160811946027</v>
       </c>
       <c r="F23" t="n">
         <v>406.8760457417114</v>
@@ -24181,10 +24181,10 @@
         <v>415.302737515135</v>
       </c>
       <c r="H23" t="n">
-        <v>108.6271810407856</v>
+        <v>339.4748021157671</v>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
+        <v>10.13979328157632</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -24220,10 +24220,10 @@
         <v>223.0958495641314</v>
       </c>
       <c r="U23" t="n">
-        <v>251.3456529078365</v>
+        <v>10.33136403017744</v>
       </c>
       <c r="V23" t="n">
-        <v>86.7522584701349</v>
+        <v>86.73796959247585</v>
       </c>
       <c r="W23" t="n">
         <v>349.240968717413</v>
@@ -24251,7 +24251,7 @@
         <v>147.4450655646388</v>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>157.6450804554009</v>
       </c>
       <c r="F24" t="n">
         <v>145.0692123933839</v>
@@ -24260,10 +24260,10 @@
         <v>137.3435171632106</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="I24" t="n">
-        <v>1.993222173961669</v>
+        <v>18.54868025714062</v>
       </c>
       <c r="J24" t="n">
         <v>0.7465913262578567</v>
@@ -24290,16 +24290,16 @@
         <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>100.1578341526431</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>171.6831711038378</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>200.1647286948216</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>225.9413820809748</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
         <v>232.8005871494253</v>
@@ -24308,10 +24308,10 @@
         <v>251.6949831609196</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>205.7729852034775</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>205.6826957773044</v>
       </c>
     </row>
     <row r="25">
@@ -24342,13 +24342,13 @@
         <v>162.2271725074396</v>
       </c>
       <c r="I25" t="n">
-        <v>137.8921792844459</v>
+        <v>155.4504749272583</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="K25" t="n">
-        <v>0</v>
+        <v>22.26949182588285</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
@@ -24390,7 +24390,7 @@
         <v>225.7096553890372</v>
       </c>
       <c r="Y25" t="n">
-        <v>218.5846533520948</v>
+        <v>85.39768576672677</v>
       </c>
     </row>
     <row r="26">
@@ -24445,31 +24445,31 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>9.990699214544804</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>149.8691179411497</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>138.6760617849701</v>
       </c>
       <c r="T26" t="n">
-        <v>223.0958495641314</v>
+        <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>10.3456529078365</v>
+        <v>251.3456529078365</v>
       </c>
       <c r="V26" t="n">
-        <v>86.7522584701349</v>
+        <v>327.7522584701349</v>
       </c>
       <c r="W26" t="n">
-        <v>108.240968717413</v>
+        <v>108.226679839754</v>
       </c>
       <c r="X26" t="n">
-        <v>366.4783702647144</v>
+        <v>369.731100678469</v>
       </c>
       <c r="Y26" t="n">
-        <v>386.2379386560536</v>
+        <v>145.2236497783945</v>
       </c>
     </row>
     <row r="27">
@@ -24479,16 +24479,16 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>166.5331836498673</v>
+        <v>0</v>
       </c>
       <c r="C27" t="n">
-        <v>127.4750771317625</v>
+        <v>172.7084989883157</v>
       </c>
       <c r="D27" t="n">
-        <v>0</v>
+        <v>147.4450655646388</v>
       </c>
       <c r="E27" t="n">
-        <v>0</v>
+        <v>157.6450804554009</v>
       </c>
       <c r="F27" t="n">
         <v>0</v>
@@ -24497,10 +24497,10 @@
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>9.60830957984156</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -24527,13 +24527,13 @@
         <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>100.1578341526431</v>
       </c>
       <c r="S27" t="n">
         <v>171.6831711038378</v>
       </c>
       <c r="T27" t="n">
-        <v>200.1647286948216</v>
+        <v>0</v>
       </c>
       <c r="U27" t="n">
         <v>225.9413820809748</v>
@@ -24548,7 +24548,7 @@
         <v>205.7729852034775</v>
       </c>
       <c r="Y27" t="n">
-        <v>205.6826957773044</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -24585,7 +24585,7 @@
         <v>93.35918011667277</v>
       </c>
       <c r="K28" t="n">
-        <v>0</v>
+        <v>22.26949182588285</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
@@ -24615,10 +24615,10 @@
         <v>227.9455894282815</v>
       </c>
       <c r="U28" t="n">
-        <v>175.4015535970057</v>
+        <v>286.3190293564909</v>
       </c>
       <c r="V28" t="n">
-        <v>252.137643323828</v>
+        <v>118.95067573846</v>
       </c>
       <c r="W28" t="n">
         <v>286.522998336591</v>
@@ -24652,7 +24652,7 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G29" t="n">
-        <v>415.302737515135</v>
+        <v>185.0989125581653</v>
       </c>
       <c r="H29" t="n">
         <v>339.4748021157671</v>
@@ -24685,10 +24685,10 @@
         <v>9.990699214544804</v>
       </c>
       <c r="R29" t="n">
-        <v>128.7122370915265</v>
+        <v>149.8691179411497</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>209.0200695862453</v>
       </c>
       <c r="T29" t="n">
         <v>0</v>
@@ -24697,16 +24697,16 @@
         <v>251.3456529078365</v>
       </c>
       <c r="V29" t="n">
-        <v>86.7522584701349</v>
+        <v>327.7522584701349</v>
       </c>
       <c r="W29" t="n">
-        <v>108.240968717413</v>
+        <v>349.240968717413</v>
       </c>
       <c r="X29" t="n">
-        <v>369.731100678469</v>
+        <v>128.71681180081</v>
       </c>
       <c r="Y29" t="n">
-        <v>386.2379386560536</v>
+        <v>145.2236497783945</v>
       </c>
     </row>
     <row r="30">
@@ -24716,28 +24716,28 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>166.5331836498673</v>
+        <v>0</v>
       </c>
       <c r="C30" t="n">
-        <v>26.57065165286144</v>
+        <v>0</v>
       </c>
       <c r="D30" t="n">
         <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
+        <v>157.6450804554009</v>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="I30" t="n">
-        <v>0</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="J30" t="n">
         <v>0.7465913262578567</v>
@@ -24764,7 +24764,7 @@
         <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>100.1578341526431</v>
+        <v>62.97201105982758</v>
       </c>
       <c r="S30" t="n">
         <v>171.6831711038378</v>
@@ -24782,10 +24782,10 @@
         <v>251.6949831609196</v>
       </c>
       <c r="X30" t="n">
-        <v>205.7729852034775</v>
+        <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>205.6826957773044</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -24813,16 +24813,16 @@
         <v>167.9909793584588</v>
       </c>
       <c r="H31" t="n">
-        <v>162.2271725074396</v>
+        <v>29.04020492207155</v>
       </c>
       <c r="I31" t="n">
-        <v>137.8921792844459</v>
+        <v>155.4504749272583</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="K31" t="n">
-        <v>0</v>
+        <v>22.26949182588285</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
@@ -24880,10 +24880,10 @@
         <v>365.2728917710076</v>
       </c>
       <c r="D32" t="n">
-        <v>139.683041620683</v>
+        <v>354.683041620683</v>
       </c>
       <c r="E32" t="n">
-        <v>166.9303700722618</v>
+        <v>381.9303700722618</v>
       </c>
       <c r="F32" t="n">
         <v>406.8760457417114</v>
@@ -24919,25 +24919,25 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>149.8691179411497</v>
       </c>
       <c r="S32" t="n">
-        <v>179.5078867419399</v>
+        <v>209.0200695862453</v>
       </c>
       <c r="T32" t="n">
-        <v>223.0958495641314</v>
+        <v>10.81046392068936</v>
       </c>
       <c r="U32" t="n">
-        <v>251.3456529078365</v>
+        <v>10.33136403017744</v>
       </c>
       <c r="V32" t="n">
-        <v>112.7522584701349</v>
+        <v>86.73796959247585</v>
       </c>
       <c r="W32" t="n">
-        <v>349.240968717413</v>
+        <v>108.226679839754</v>
       </c>
       <c r="X32" t="n">
         <v>369.731100678469</v>
@@ -24953,31 +24953,31 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0</v>
+        <v>166.5331836498673</v>
       </c>
       <c r="C33" t="n">
-        <v>172.7084989883157</v>
+        <v>0</v>
       </c>
       <c r="D33" t="n">
         <v>147.4450655646388</v>
       </c>
       <c r="E33" t="n">
-        <v>157.6450804554009</v>
+        <v>79.98145383288308</v>
       </c>
       <c r="F33" t="n">
-        <v>145.0692123933839</v>
+        <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>137.3435171632106</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>112.2354442364965</v>
+        <v>0</v>
       </c>
       <c r="I33" t="n">
         <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>0.7465913262578567</v>
+        <v>0</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
@@ -25004,13 +25004,13 @@
         <v>100.1578341526431</v>
       </c>
       <c r="S33" t="n">
-        <v>13.9236833824246</v>
+        <v>171.6831711038378</v>
       </c>
       <c r="T33" t="n">
-        <v>200.1647286948216</v>
+        <v>0</v>
       </c>
       <c r="U33" t="n">
-        <v>10.94138208097482</v>
+        <v>225.9413820809748</v>
       </c>
       <c r="V33" t="n">
         <v>232.8005871494253</v>
@@ -25022,7 +25022,7 @@
         <v>205.7729852034775</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>205.6826957773044</v>
       </c>
     </row>
     <row r="34">
@@ -25053,13 +25053,13 @@
         <v>162.2271725074396</v>
       </c>
       <c r="I34" t="n">
-        <v>155.4504749272583</v>
+        <v>137.8921792844459</v>
       </c>
       <c r="J34" t="n">
-        <v>93.35918011667277</v>
+        <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>22.26949182588285</v>
+        <v>0</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
@@ -25074,16 +25074,16 @@
         <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>2.721440735106512</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>86.16204325169439</v>
       </c>
       <c r="R34" t="n">
         <v>177.2933913771695</v>
       </c>
       <c r="S34" t="n">
-        <v>179.7131144384051</v>
+        <v>224.0165980369723</v>
       </c>
       <c r="T34" t="n">
         <v>227.9455894282815</v>
@@ -25114,10 +25114,10 @@
         <v>382.7338416634806</v>
       </c>
       <c r="C35" t="n">
-        <v>150.2728917710076</v>
+        <v>365.2728917710076</v>
       </c>
       <c r="D35" t="n">
-        <v>165.311041620683</v>
+        <v>354.683041620683</v>
       </c>
       <c r="E35" t="n">
         <v>381.9303700722618</v>
@@ -25168,19 +25168,19 @@
         <v>223.0958495641314</v>
       </c>
       <c r="U35" t="n">
-        <v>251.3456529078365</v>
+        <v>39.0602672643945</v>
       </c>
       <c r="V35" t="n">
-        <v>112.7522584701349</v>
+        <v>327.7522584701349</v>
       </c>
       <c r="W35" t="n">
-        <v>349.240968717413</v>
+        <v>108.226679839754</v>
       </c>
       <c r="X35" t="n">
-        <v>369.731100678469</v>
+        <v>128.71681180081</v>
       </c>
       <c r="Y35" t="n">
-        <v>171.2379386560536</v>
+        <v>145.2236497783945</v>
       </c>
     </row>
     <row r="36">
@@ -25199,16 +25199,16 @@
         <v>147.4450655646388</v>
       </c>
       <c r="E36" t="n">
-        <v>157.6450804554009</v>
+        <v>0</v>
       </c>
       <c r="F36" t="n">
         <v>145.0692123933839</v>
       </c>
       <c r="G36" t="n">
-        <v>108.0586845656959</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H36" t="n">
-        <v>0</v>
+        <v>64.3596665401007</v>
       </c>
       <c r="I36" t="n">
         <v>0</v>
@@ -25247,13 +25247,13 @@
         <v>200.1647286948216</v>
       </c>
       <c r="U36" t="n">
-        <v>10.94138208097482</v>
+        <v>0</v>
       </c>
       <c r="V36" t="n">
         <v>232.8005871494253</v>
       </c>
       <c r="W36" t="n">
-        <v>36.69498316091961</v>
+        <v>10.68069428326055</v>
       </c>
       <c r="X36" t="n">
         <v>205.7729852034775</v>
@@ -25278,7 +25278,7 @@
         <v>148.6154730182124</v>
       </c>
       <c r="E37" t="n">
-        <v>146.4339626465692</v>
+        <v>13.24699506120118</v>
       </c>
       <c r="F37" t="n">
         <v>145.4210480229312</v>
@@ -25320,7 +25320,7 @@
         <v>177.2933913771695</v>
       </c>
       <c r="S37" t="n">
-        <v>90.8296304516042</v>
+        <v>224.0165980369723</v>
       </c>
       <c r="T37" t="n">
         <v>227.9455894282815</v>
@@ -25363,16 +25363,16 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G38" t="n">
-        <v>415.302737515135</v>
+        <v>174.288448637476</v>
       </c>
       <c r="H38" t="n">
-        <v>339.4748021157671</v>
+        <v>98.46051323810809</v>
       </c>
       <c r="I38" t="n">
-        <v>21.10388957040598</v>
+        <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>11.94928935461252</v>
+        <v>0</v>
       </c>
       <c r="K38" t="n">
         <v>0</v>
@@ -25393,19 +25393,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>9.990699214544804</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>149.8691179411497</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>209.0200695862453</v>
+        <v>138.0053911458572</v>
       </c>
       <c r="T38" t="n">
-        <v>8.095849564131356</v>
+        <v>223.0958495641314</v>
       </c>
       <c r="U38" t="n">
-        <v>36.3456529078365</v>
+        <v>251.3456529078365</v>
       </c>
       <c r="V38" t="n">
         <v>327.7522584701349</v>
@@ -25417,7 +25417,7 @@
         <v>369.731100678469</v>
       </c>
       <c r="Y38" t="n">
-        <v>171.2379386560536</v>
+        <v>386.2379386560536</v>
       </c>
     </row>
     <row r="39">
@@ -25430,19 +25430,19 @@
         <v>166.5331836498673</v>
       </c>
       <c r="C39" t="n">
-        <v>0</v>
+        <v>172.7084989883157</v>
       </c>
       <c r="D39" t="n">
-        <v>0</v>
+        <v>147.4450655646388</v>
       </c>
       <c r="E39" t="n">
-        <v>0</v>
+        <v>157.6450804554009</v>
       </c>
       <c r="F39" t="n">
-        <v>0</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="G39" t="n">
-        <v>126.0041032597716</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H39" t="n">
         <v>112.2354442364965</v>
@@ -25478,22 +25478,22 @@
         <v>100.1578341526431</v>
       </c>
       <c r="S39" t="n">
-        <v>171.6831711038378</v>
+        <v>0</v>
       </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>101.0346019561178</v>
       </c>
       <c r="U39" t="n">
-        <v>225.9413820809748</v>
+        <v>0</v>
       </c>
       <c r="V39" t="n">
-        <v>232.8005871494253</v>
+        <v>0</v>
       </c>
       <c r="W39" t="n">
         <v>251.6949831609196</v>
       </c>
       <c r="X39" t="n">
-        <v>205.7729852034775</v>
+        <v>0</v>
       </c>
       <c r="Y39" t="n">
         <v>205.6826957773044</v>
@@ -25512,7 +25512,7 @@
         <v>167.2468210986278</v>
       </c>
       <c r="D40" t="n">
-        <v>148.6154730182124</v>
+        <v>15.42850543284433</v>
       </c>
       <c r="E40" t="n">
         <v>146.4339626465692</v>
@@ -25563,7 +25563,7 @@
         <v>227.9455894282815</v>
       </c>
       <c r="U40" t="n">
-        <v>153.1320617711228</v>
+        <v>286.3190293564909</v>
       </c>
       <c r="V40" t="n">
         <v>252.137643323828</v>
@@ -25591,13 +25591,13 @@
         <v>365.2728917710076</v>
       </c>
       <c r="D41" t="n">
-        <v>354.683041620683</v>
+        <v>141.25877800334</v>
       </c>
       <c r="E41" t="n">
-        <v>168.9303700722618</v>
+        <v>381.9303700722618</v>
       </c>
       <c r="F41" t="n">
-        <v>406.8760457417114</v>
+        <v>193.4517821243685</v>
       </c>
       <c r="G41" t="n">
         <v>415.302737515135</v>
@@ -25630,7 +25630,7 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>9.990699214544804</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
         <v>149.8691179411497</v>
@@ -25639,16 +25639,16 @@
         <v>209.0200695862453</v>
       </c>
       <c r="T41" t="n">
-        <v>223.0958495641314</v>
+        <v>45.10245738452056</v>
       </c>
       <c r="U41" t="n">
-        <v>63.7352529078365</v>
+        <v>251.3456529078365</v>
       </c>
       <c r="V41" t="n">
-        <v>114.7522584701349</v>
+        <v>114.327994852792</v>
       </c>
       <c r="W41" t="n">
-        <v>136.240968717413</v>
+        <v>349.240968717413</v>
       </c>
       <c r="X41" t="n">
         <v>369.731100678469</v>
@@ -25670,19 +25670,19 @@
         <v>172.7084989883157</v>
       </c>
       <c r="D42" t="n">
-        <v>0</v>
+        <v>147.4450655646388</v>
       </c>
       <c r="E42" t="n">
-        <v>86.12791981313065</v>
+        <v>91.611659970552</v>
       </c>
       <c r="F42" t="n">
-        <v>0</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>0</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="I42" t="n">
         <v>89.39663285141508</v>
@@ -25721,19 +25721,19 @@
         <v>200.1647286948216</v>
       </c>
       <c r="U42" t="n">
-        <v>225.9413820809748</v>
+        <v>12.5171184636319</v>
       </c>
       <c r="V42" t="n">
         <v>232.8005871494253</v>
       </c>
       <c r="W42" t="n">
-        <v>38.69498316091961</v>
+        <v>251.6949831609196</v>
       </c>
       <c r="X42" t="n">
-        <v>205.7729852034775</v>
+        <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>205.6826957773044</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -25806,13 +25806,13 @@
         <v>252.137643323828</v>
       </c>
       <c r="W43" t="n">
-        <v>286.522998336591</v>
+        <v>153.336030751223</v>
       </c>
       <c r="X43" t="n">
         <v>225.7096553890372</v>
       </c>
       <c r="Y43" t="n">
-        <v>85.39768576672677</v>
+        <v>218.5846533520948</v>
       </c>
     </row>
     <row r="44">
@@ -26094,7 +26094,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>350365.0263125471</v>
+        <v>327897.5868709115</v>
       </c>
     </row>
     <row r="5">
@@ -26102,7 +26102,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>350365.0263125471</v>
+        <v>327897.5868709115</v>
       </c>
     </row>
     <row r="6">
@@ -26110,7 +26110,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>350365.0263125471</v>
+        <v>327897.5868709115</v>
       </c>
     </row>
     <row r="7">
@@ -26118,7 +26118,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>352010.6902785869</v>
+        <v>351685.049566824</v>
       </c>
     </row>
     <row r="8">
@@ -26126,7 +26126,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>506898.8173466544</v>
+        <v>506909.1411107077</v>
       </c>
     </row>
     <row r="9">
@@ -26134,7 +26134,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>506898.8173466544</v>
+        <v>506909.1411107077</v>
       </c>
     </row>
     <row r="10">
@@ -26142,7 +26142,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>506898.8173466544</v>
+        <v>506909.1411107077</v>
       </c>
     </row>
     <row r="11">
@@ -26150,7 +26150,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>506898.8173466544</v>
+        <v>506909.1411107077</v>
       </c>
     </row>
     <row r="12">
@@ -26158,7 +26158,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>488113.7264674625</v>
+        <v>506909.1411107077</v>
       </c>
     </row>
     <row r="13">
@@ -26166,7 +26166,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>488113.7264674625</v>
+        <v>506909.1411107077</v>
       </c>
     </row>
     <row r="14">
@@ -26174,7 +26174,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>488113.7264674625</v>
+        <v>506909.1411107077</v>
       </c>
     </row>
     <row r="15">
@@ -26182,7 +26182,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>486668.7194767555</v>
+        <v>486975.2514232371</v>
       </c>
     </row>
     <row r="16">
@@ -26267,40 +26267,40 @@
         <v>59129.07304229552</v>
       </c>
       <c r="D2" t="n">
-        <v>63177.88319582793</v>
+        <v>59129.07304229552</v>
       </c>
       <c r="E2" t="n">
-        <v>63177.88319582795</v>
+        <v>59129.07304229552</v>
       </c>
       <c r="F2" t="n">
-        <v>63177.88319582796</v>
+        <v>59129.07304229552</v>
       </c>
       <c r="G2" t="n">
-        <v>63474.44484862835</v>
+        <v>63415.76181874351</v>
       </c>
       <c r="H2" t="n">
-        <v>91386.50946835899</v>
+        <v>91388.36989223282</v>
       </c>
       <c r="I2" t="n">
-        <v>91386.50946835897</v>
+        <v>91388.3698922328</v>
       </c>
       <c r="J2" t="n">
-        <v>91386.50946835899</v>
+        <v>91388.36989223279</v>
       </c>
       <c r="K2" t="n">
-        <v>91386.50946835894</v>
+        <v>91388.36989223279</v>
       </c>
       <c r="L2" t="n">
-        <v>88001.28762835894</v>
+        <v>91388.36989223279</v>
       </c>
       <c r="M2" t="n">
-        <v>88001.28762835896</v>
+        <v>91388.3698922328</v>
       </c>
       <c r="N2" t="n">
-        <v>88001.28762835893</v>
+        <v>91388.36989223285</v>
       </c>
       <c r="O2" t="n">
-        <v>87740.88594835895</v>
+        <v>87796.12542771843</v>
       </c>
       <c r="P2" t="n">
         <v>59129.07304229552</v>
@@ -26319,7 +26319,7 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>8076.38</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -26328,10 +26328,10 @@
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>548.1700000000001</v>
+        <v>7562.01207347375</v>
       </c>
       <c r="H3" t="n">
-        <v>57469.317</v>
+        <v>57583.78714233168</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -26365,49 +26365,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>10750.74055314464</v>
+        <v>12588.27138056849</v>
       </c>
       <c r="C4" t="n">
-        <v>10750.74055314464</v>
+        <v>12588.27138056849</v>
       </c>
       <c r="D4" t="n">
-        <v>11524.36744801407</v>
+        <v>12588.27138056849</v>
       </c>
       <c r="E4" t="n">
-        <v>11524.36744801407</v>
+        <v>12588.27138056849</v>
       </c>
       <c r="F4" t="n">
-        <v>11524.36744801407</v>
+        <v>12588.27138056849</v>
       </c>
       <c r="G4" t="n">
-        <v>11581.0330020641</v>
+        <v>13543.27151380256</v>
       </c>
       <c r="H4" t="n">
-        <v>16914.33416026179</v>
+        <v>19775.08488543298</v>
       </c>
       <c r="I4" t="n">
-        <v>16914.33416026179</v>
+        <v>19775.08488543298</v>
       </c>
       <c r="J4" t="n">
-        <v>16914.33416026179</v>
+        <v>19775.08488543298</v>
       </c>
       <c r="K4" t="n">
-        <v>16914.33416026179</v>
+        <v>19775.08488543298</v>
       </c>
       <c r="L4" t="n">
-        <v>16267.50248349411</v>
+        <v>19775.08488543298</v>
       </c>
       <c r="M4" t="n">
-        <v>16267.50248349411</v>
+        <v>19775.08488543298</v>
       </c>
       <c r="N4" t="n">
-        <v>16267.50248349411</v>
+        <v>19775.08488543298</v>
       </c>
       <c r="O4" t="n">
-        <v>16217.74620066583</v>
+        <v>18974.79493644741</v>
       </c>
       <c r="P4" t="n">
-        <v>10750.74055314464</v>
+        <v>12588.27138056849</v>
       </c>
     </row>
     <row r="5">
@@ -26423,40 +26423,40 @@
         <v>33627.6</v>
       </c>
       <c r="D5" t="n">
-        <v>35208.4</v>
+        <v>33627.6</v>
       </c>
       <c r="E5" t="n">
-        <v>1580.8</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>1580.8</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>1702.4</v>
+        <v>1677.473535827221</v>
       </c>
       <c r="H5" t="n">
-        <v>14652.8</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="I5" t="n">
-        <v>14652.8</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="J5" t="n">
-        <v>14652.8</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="K5" t="n">
-        <v>14652.8</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="L5" t="n">
-        <v>13072</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="M5" t="n">
-        <v>13072</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="N5" t="n">
-        <v>13072</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="O5" t="n">
-        <v>12950.4</v>
+        <v>12976.19522793445</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
@@ -26469,49 +26469,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>14750.73248915088</v>
+        <v>12913.20166172703</v>
       </c>
       <c r="C6" t="n">
-        <v>14750.73248915088</v>
+        <v>12913.20166172703</v>
       </c>
       <c r="D6" t="n">
-        <v>8368.735747813858</v>
+        <v>12913.20166172703</v>
       </c>
       <c r="E6" t="n">
-        <v>50072.71574781388</v>
+        <v>46540.80166172703</v>
       </c>
       <c r="F6" t="n">
-        <v>50072.71574781389</v>
+        <v>46540.80166172703</v>
       </c>
       <c r="G6" t="n">
-        <v>49642.84184656425</v>
+        <v>40633.00469563998</v>
       </c>
       <c r="H6" t="n">
-        <v>2350.058308097196</v>
+        <v>-624.1708992935164</v>
       </c>
       <c r="I6" t="n">
-        <v>59819.37530809718</v>
+        <v>56959.61624303815</v>
       </c>
       <c r="J6" t="n">
-        <v>59819.37530809719</v>
+        <v>56959.61624303814</v>
       </c>
       <c r="K6" t="n">
-        <v>59819.37530809715</v>
+        <v>56959.61624303814</v>
       </c>
       <c r="L6" t="n">
-        <v>58661.78514486484</v>
+        <v>56959.61624303814</v>
       </c>
       <c r="M6" t="n">
-        <v>58661.78514486484</v>
+        <v>56959.61624303815</v>
       </c>
       <c r="N6" t="n">
-        <v>58661.78514486481</v>
+        <v>56959.6162430382</v>
       </c>
       <c r="O6" t="n">
-        <v>58572.73974769311</v>
+        <v>55845.13526333657</v>
       </c>
       <c r="P6" t="n">
-        <v>48378.33248915088</v>
+        <v>46540.80166172703</v>
       </c>
     </row>
   </sheetData>
@@ -26733,40 +26733,40 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>28</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="H4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="I4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="J4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="K4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="L4" t="n">
-        <v>215</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="M4" t="n">
-        <v>215</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="N4" t="n">
-        <v>215</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="O4" t="n">
-        <v>213</v>
+        <v>213.4242636173429</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
@@ -26840,49 +26840,49 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -26895,10 +26895,10 @@
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -26907,16 +26907,16 @@
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -26931,10 +26931,10 @@
         <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -26950,7 +26950,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -26959,34 +26959,34 @@
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>2</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="H4" t="n">
-        <v>213</v>
+        <v>213.4242636173429</v>
       </c>
       <c r="I4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -27191,7 +27191,7 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -27200,10 +27200,10 @@
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>2</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="P4" t="n">
-        <v>213</v>
+        <v>213.4242636173429</v>
       </c>
     </row>
   </sheetData>
@@ -35091,16 +35091,16 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>24.94949494949496</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
@@ -35170,19 +35170,19 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>24.94949494949495</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -35249,16 +35249,16 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>24.58512791403967</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
@@ -35328,19 +35328,19 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>24.94949494949496</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -35407,10 +35407,10 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -35419,10 +35419,10 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>24.94949494949495</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -35486,16 +35486,16 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>24.58512791403967</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
         <v>0</v>
@@ -35562,10 +35562,10 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -35574,10 +35574,10 @@
         <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>24.94949494949495</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -35647,19 +35647,19 @@
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>24.94949494949496</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -35723,16 +35723,16 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>24.58512791403967</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
         <v>0</v>
@@ -35799,22 +35799,22 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>26.47527676494984</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>26.86868686868687</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="N17" t="n">
-        <v>28</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="O17" t="n">
-        <v>28</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="P17" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -35881,22 +35881,22 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>26.47527676494984</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>26.86868686868687</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="O18" t="n">
-        <v>28</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="P18" t="n">
-        <v>28</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="Q18" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -35963,10 +35963,10 @@
         <v>27.59002526031614</v>
       </c>
       <c r="M19" t="n">
-        <v>28</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="N19" t="n">
-        <v>28</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="O19" t="n">
         <v>24.58512791403967</v>
@@ -36051,7 +36051,7 @@
         <v>150.7019698410586</v>
       </c>
       <c r="P20" t="n">
-        <v>90.50913423396717</v>
+        <v>90.5657124162131</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -36118,22 +36118,22 @@
         <v>126.6237980382196</v>
       </c>
       <c r="L21" t="n">
-        <v>232.285965523585</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>241</v>
+        <v>91.0829537758999</v>
       </c>
       <c r="N21" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="O21" t="n">
-        <v>113.3528627008217</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>184.4883612256069</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>70.09551364982758</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
@@ -36273,7 +36273,7 @@
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>103.9989833439383</v>
+        <v>104.0555615261842</v>
       </c>
       <c r="L23" t="n">
         <v>181.8947995804632</v>
@@ -36352,22 +36352,22 @@
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>126.6237980382196</v>
+        <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>34.54331457457899</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="N24" t="n">
-        <v>241</v>
+        <v>217.7067518141195</v>
       </c>
       <c r="O24" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>184.4883612256069</v>
       </c>
       <c r="Q24" t="n">
         <v>70.09551364982758</v>
@@ -36519,13 +36519,13 @@
         <v>219.1673002655598</v>
       </c>
       <c r="N26" t="n">
-        <v>207.9338608153932</v>
+        <v>207.9338608153933</v>
       </c>
       <c r="O26" t="n">
         <v>150.7019698410586</v>
       </c>
       <c r="P26" t="n">
-        <v>90.50913423396717</v>
+        <v>90.5657124162131</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -36589,25 +36589,25 @@
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>126.6237980382196</v>
+        <v>0</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="N27" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="O27" t="n">
-        <v>161.1504669987997</v>
+        <v>217.7067518141195</v>
       </c>
       <c r="P27" t="n">
         <v>184.4883612256069</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>70.09551364982758</v>
       </c>
       <c r="R27" t="n">
         <v>0</v>
@@ -36756,7 +36756,7 @@
         <v>219.1673002655598</v>
       </c>
       <c r="N29" t="n">
-        <v>207.8772826331474</v>
+        <v>207.9338608153933</v>
       </c>
       <c r="O29" t="n">
         <v>150.7019698410586</v>
@@ -36829,16 +36829,16 @@
         <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>217.6787513871916</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="N30" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="O30" t="n">
-        <v>241</v>
+        <v>217.7067518141195</v>
       </c>
       <c r="P30" t="n">
         <v>184.4883612256069</v>
@@ -36987,10 +36987,10 @@
         <v>104.0555615261842</v>
       </c>
       <c r="L32" t="n">
-        <v>83.05602671428214</v>
+        <v>181.8947995804632</v>
       </c>
       <c r="M32" t="n">
-        <v>215</v>
+        <v>219.1673002655598</v>
       </c>
       <c r="N32" t="n">
         <v>207.9338608153932</v>
@@ -37066,16 +37066,16 @@
         <v>126.6237980382196</v>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>91.0829537758999</v>
       </c>
       <c r="M33" t="n">
-        <v>215</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="N33" t="n">
-        <v>40.10545839947712</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="O33" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="P33" t="n">
         <v>184.4883612256069</v>
@@ -37227,13 +37227,13 @@
         <v>181.8947995804632</v>
       </c>
       <c r="M35" t="n">
-        <v>215</v>
+        <v>219.1673002655598</v>
       </c>
       <c r="N35" t="n">
-        <v>207.9338608153932</v>
+        <v>207.9338608153933</v>
       </c>
       <c r="O35" t="n">
-        <v>51.86319697487763</v>
+        <v>150.7019698410586</v>
       </c>
       <c r="P35" t="n">
         <v>90.5657124162131</v>
@@ -37303,16 +37303,16 @@
         <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>217.7067518141195</v>
       </c>
       <c r="M36" t="n">
-        <v>166.7292564376967</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="N36" t="n">
-        <v>215</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="O36" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="P36" t="n">
         <v>184.4883612256069</v>
@@ -37464,16 +37464,16 @@
         <v>181.8947995804632</v>
       </c>
       <c r="M38" t="n">
-        <v>215</v>
+        <v>219.1673002655598</v>
       </c>
       <c r="N38" t="n">
         <v>207.9338608153932</v>
       </c>
       <c r="O38" t="n">
-        <v>142.4289093910907</v>
+        <v>150.7019698410586</v>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>90.5657124162131</v>
       </c>
       <c r="Q38" t="n">
         <v>0</v>
@@ -37540,22 +37540,22 @@
         <v>0</v>
       </c>
       <c r="L39" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>215</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="N39" t="n">
-        <v>215</v>
+        <v>217.7067518141195</v>
       </c>
       <c r="O39" t="n">
-        <v>206.3131313131313</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>184.4883612256069</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>70.09551364982758</v>
       </c>
       <c r="R39" t="n">
         <v>0</v>
@@ -37695,22 +37695,22 @@
         <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>104.0555615261842</v>
+        <v>0.5532456285028686</v>
       </c>
       <c r="L41" t="n">
         <v>181.8947995804632</v>
       </c>
       <c r="M41" t="n">
-        <v>213</v>
+        <v>213.4242636173429</v>
       </c>
       <c r="N41" t="n">
         <v>207.9338608153932</v>
       </c>
       <c r="O41" t="n">
-        <v>136.5097174718987</v>
+        <v>150.7019698410586</v>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>90.5657124162131</v>
       </c>
       <c r="Q41" t="n">
         <v>0</v>
@@ -37777,22 +37777,22 @@
         <v>126.6237980382196</v>
       </c>
       <c r="L42" t="n">
-        <v>213</v>
+        <v>213.4242636173429</v>
       </c>
       <c r="M42" t="n">
-        <v>213</v>
+        <v>213.4242636173429</v>
       </c>
       <c r="N42" t="n">
-        <v>77.7701413557198</v>
+        <v>213.4242636173429</v>
       </c>
       <c r="O42" t="n">
-        <v>213</v>
+        <v>8.081749358897964</v>
       </c>
       <c r="P42" t="n">
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>70.09551364982758</v>
       </c>
       <c r="R42" t="n">
         <v>0</v>
